--- a/data/exports/accounts_opened_merged.xlsx
+++ b/data/exports/accounts_opened_merged.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,53 +413,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1062"/>
+  <dimension ref="A1:O1093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="n">
+      <c r="A1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" t="n">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" t="n">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" t="n">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" t="n">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" t="n">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" t="n">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="N1" t="n">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="O1" t="n">
         <v>14</v>
       </c>
     </row>
@@ -30148,27 +30136,23 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>Bahu SO</t>
+          <t>Assaudha SO</t>
         </is>
       </c>
       <c r="B928" t="n">
-        <v>12414201</v>
+        <v>12450501</v>
       </c>
       <c r="C928" t="inlineStr"/>
       <c r="D928" t="inlineStr"/>
       <c r="E928" t="inlineStr"/>
       <c r="F928" t="inlineStr"/>
       <c r="G928" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H928" t="inlineStr"/>
-      <c r="I928" t="n">
-        <v>2</v>
-      </c>
+      <c r="I928" t="inlineStr"/>
       <c r="J928" t="inlineStr"/>
-      <c r="K928" t="n">
-        <v>1</v>
-      </c>
+      <c r="K928" t="inlineStr"/>
       <c r="L928" t="inlineStr"/>
       <c r="M928" t="inlineStr"/>
       <c r="N928" t="inlineStr"/>
@@ -30177,31 +30161,29 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>Beri SO</t>
-        </is>
-      </c>
-      <c r="B929" t="n">
-        <v>12420101</v>
-      </c>
-      <c r="C929" t="inlineStr"/>
-      <c r="D929" t="n">
-        <v>1</v>
-      </c>
+          <t>Atail BO</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>L5365</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Sampla SO</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr"/>
       <c r="E929" t="inlineStr"/>
-      <c r="F929" t="n">
-        <v>1</v>
-      </c>
-      <c r="G929" t="n">
-        <v>1</v>
-      </c>
+      <c r="F929" t="inlineStr"/>
+      <c r="G929" t="inlineStr"/>
       <c r="H929" t="inlineStr"/>
       <c r="I929" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J929" t="inlineStr"/>
-      <c r="K929" t="n">
-        <v>9</v>
-      </c>
+      <c r="K929" t="inlineStr"/>
       <c r="L929" t="inlineStr"/>
       <c r="M929" t="inlineStr"/>
       <c r="N929" t="inlineStr"/>
@@ -30210,30 +30192,22 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>Birdhana BO</t>
-        </is>
-      </c>
-      <c r="B930" t="inlineStr">
-        <is>
-          <t>D7057</t>
-        </is>
-      </c>
-      <c r="C930" t="inlineStr">
-        <is>
-          <t>Dujana SO</t>
-        </is>
-      </c>
+          <t>Badli SO Jhajjar</t>
+        </is>
+      </c>
+      <c r="B930" t="n">
+        <v>12410501</v>
+      </c>
+      <c r="C930" t="inlineStr"/>
       <c r="D930" t="inlineStr"/>
       <c r="E930" t="inlineStr"/>
-      <c r="F930" t="n">
-        <v>1</v>
-      </c>
+      <c r="F930" t="inlineStr"/>
       <c r="G930" t="inlineStr"/>
       <c r="H930" t="inlineStr"/>
       <c r="I930" t="inlineStr"/>
       <c r="J930" t="inlineStr"/>
       <c r="K930" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L930" t="inlineStr"/>
       <c r="M930" t="inlineStr"/>
@@ -30243,65 +30217,59 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>Bishan BO</t>
-        </is>
-      </c>
-      <c r="B931" t="inlineStr">
-        <is>
-          <t>A3311</t>
-        </is>
-      </c>
-      <c r="C931" t="inlineStr">
-        <is>
-          <t>Beri SO</t>
-        </is>
-      </c>
-      <c r="D931" t="inlineStr"/>
+          <t>Bahadurgarh HO</t>
+        </is>
+      </c>
+      <c r="B931" t="n">
+        <v>12450700</v>
+      </c>
+      <c r="C931" t="inlineStr"/>
+      <c r="D931" t="n">
+        <v>1</v>
+      </c>
       <c r="E931" t="inlineStr"/>
       <c r="F931" t="inlineStr"/>
-      <c r="G931" t="inlineStr"/>
+      <c r="G931" t="n">
+        <v>4</v>
+      </c>
       <c r="H931" t="inlineStr"/>
       <c r="I931" t="n">
         <v>1</v>
       </c>
-      <c r="J931" t="inlineStr"/>
+      <c r="J931" t="n">
+        <v>1</v>
+      </c>
       <c r="K931" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L931" t="inlineStr"/>
-      <c r="M931" t="inlineStr"/>
-      <c r="N931" t="inlineStr"/>
+      <c r="M931" t="n">
+        <v>1</v>
+      </c>
+      <c r="N931" t="n">
+        <v>2</v>
+      </c>
       <c r="O931" t="inlineStr"/>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>Chhappar BO</t>
-        </is>
-      </c>
-      <c r="B932" t="inlineStr">
-        <is>
-          <t>B3544</t>
-        </is>
-      </c>
-      <c r="C932" t="inlineStr">
-        <is>
-          <t>Machrauli SO</t>
-        </is>
-      </c>
+          <t>Bahadurgarh Mandi SO</t>
+        </is>
+      </c>
+      <c r="B932" t="n">
+        <v>12450801</v>
+      </c>
+      <c r="C932" t="inlineStr"/>
       <c r="D932" t="inlineStr"/>
       <c r="E932" t="inlineStr"/>
-      <c r="F932" t="n">
-        <v>5</v>
-      </c>
-      <c r="G932" t="n">
-        <v>1</v>
-      </c>
+      <c r="F932" t="inlineStr"/>
+      <c r="G932" t="inlineStr"/>
       <c r="H932" t="inlineStr"/>
       <c r="I932" t="inlineStr"/>
       <c r="J932" t="inlineStr"/>
       <c r="K932" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L932" t="inlineStr"/>
       <c r="M932" t="inlineStr"/>
@@ -30311,44 +30279,46 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>Court Complex Jhajjar SO</t>
+          <t>Bahadurgarh Sector 6 SO</t>
         </is>
       </c>
       <c r="B933" t="n">
-        <v>12410301</v>
+        <v>12450702</v>
       </c>
       <c r="C933" t="inlineStr"/>
       <c r="D933" t="inlineStr"/>
       <c r="E933" t="inlineStr"/>
       <c r="F933" t="inlineStr"/>
-      <c r="G933" t="inlineStr"/>
+      <c r="G933" t="n">
+        <v>2</v>
+      </c>
       <c r="H933" t="inlineStr"/>
-      <c r="I933" t="n">
-        <v>1</v>
-      </c>
-      <c r="J933" t="inlineStr"/>
-      <c r="K933" t="n">
-        <v>1</v>
-      </c>
+      <c r="I933" t="inlineStr"/>
+      <c r="J933" t="n">
+        <v>1</v>
+      </c>
+      <c r="K933" t="inlineStr"/>
       <c r="L933" t="inlineStr"/>
       <c r="M933" t="inlineStr"/>
-      <c r="N933" t="inlineStr"/>
+      <c r="N933" t="n">
+        <v>1</v>
+      </c>
       <c r="O933" t="inlineStr"/>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>Darauli BO</t>
+          <t>Bakheta BO</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>J3750</t>
+          <t>H3439</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>Dhakla SO</t>
+          <t>Kansala SO</t>
         </is>
       </c>
       <c r="D934" t="inlineStr"/>
@@ -30357,7 +30327,7 @@
       <c r="G934" t="inlineStr"/>
       <c r="H934" t="inlineStr"/>
       <c r="I934" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J934" t="inlineStr"/>
       <c r="K934" t="inlineStr"/>
@@ -30369,13 +30339,19 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>Dhakla SO</t>
-        </is>
-      </c>
-      <c r="B935" t="n">
-        <v>12410901</v>
-      </c>
-      <c r="C935" t="inlineStr"/>
+          <t>Bamnoli BO</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>N9644</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Assaudha SO</t>
+        </is>
+      </c>
       <c r="D935" t="inlineStr"/>
       <c r="E935" t="inlineStr"/>
       <c r="F935" t="inlineStr"/>
@@ -30383,12 +30359,8 @@
         <v>1</v>
       </c>
       <c r="H935" t="inlineStr"/>
-      <c r="I935" t="n">
-        <v>0</v>
-      </c>
-      <c r="J935" t="n">
-        <v>1</v>
-      </c>
+      <c r="I935" t="inlineStr"/>
+      <c r="J935" t="inlineStr"/>
       <c r="K935" t="inlineStr"/>
       <c r="L935" t="inlineStr"/>
       <c r="M935" t="inlineStr"/>
@@ -30398,27 +30370,29 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>Dighal SO</t>
-        </is>
-      </c>
-      <c r="B936" t="n">
-        <v>12410701</v>
-      </c>
-      <c r="C936" t="inlineStr"/>
+          <t>Bohar BO</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>J7015</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Asthal Bohar SO</t>
+        </is>
+      </c>
       <c r="D936" t="inlineStr"/>
       <c r="E936" t="inlineStr"/>
       <c r="F936" t="inlineStr"/>
       <c r="G936" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H936" t="inlineStr"/>
-      <c r="I936" t="n">
-        <v>1</v>
-      </c>
+      <c r="I936" t="inlineStr"/>
       <c r="J936" t="inlineStr"/>
-      <c r="K936" t="n">
-        <v>4</v>
-      </c>
+      <c r="K936" t="inlineStr"/>
       <c r="L936" t="inlineStr"/>
       <c r="M936" t="inlineStr"/>
       <c r="N936" t="inlineStr"/>
@@ -30427,23 +30401,21 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>Dubaldhan SO</t>
+          <t>Charra SO</t>
         </is>
       </c>
       <c r="B937" t="n">
-        <v>12420201</v>
+        <v>12450401</v>
       </c>
       <c r="C937" t="inlineStr"/>
       <c r="D937" t="inlineStr"/>
       <c r="E937" t="inlineStr"/>
       <c r="F937" t="inlineStr"/>
       <c r="G937" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H937" t="inlineStr"/>
-      <c r="I937" t="n">
-        <v>1</v>
-      </c>
+      <c r="I937" t="inlineStr"/>
       <c r="J937" t="inlineStr"/>
       <c r="K937" t="n">
         <v>3</v>
@@ -30456,26 +30428,28 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>Dujana SO</t>
-        </is>
-      </c>
-      <c r="B938" t="n">
-        <v>12410201</v>
-      </c>
-      <c r="C938" t="inlineStr"/>
+          <t>Daboda Kalan BO</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>L9899</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Bahadurgarh Mandi SO</t>
+        </is>
+      </c>
       <c r="D938" t="inlineStr"/>
       <c r="E938" t="inlineStr"/>
-      <c r="F938" t="n">
-        <v>0</v>
-      </c>
-      <c r="G938" t="n">
-        <v>0</v>
-      </c>
+      <c r="F938" t="inlineStr"/>
+      <c r="G938" t="inlineStr"/>
       <c r="H938" t="inlineStr"/>
       <c r="I938" t="inlineStr"/>
       <c r="J938" t="inlineStr"/>
       <c r="K938" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L938" t="inlineStr"/>
       <c r="M938" t="inlineStr"/>
@@ -30485,17 +30459,17 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>Jahangirpur BO</t>
+          <t>Dhamar BO</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>N9278</t>
+          <t>J7278</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Nehru College Jhajjar SO</t>
+          <t>Bhalaut SO</t>
         </is>
       </c>
       <c r="D939" t="inlineStr"/>
@@ -30506,7 +30480,7 @@
       <c r="I939" t="inlineStr"/>
       <c r="J939" t="inlineStr"/>
       <c r="K939" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L939" t="inlineStr"/>
       <c r="M939" t="inlineStr"/>
@@ -30516,52 +30490,50 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>Jhajjar SO</t>
-        </is>
-      </c>
-      <c r="B940" t="n">
-        <v>12410302</v>
-      </c>
-      <c r="C940" t="inlineStr"/>
-      <c r="D940" t="n">
-        <v>1</v>
-      </c>
-      <c r="E940" t="n">
-        <v>1</v>
-      </c>
+          <t>Gandhra BO</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>L5370</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Sampla SO</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr"/>
+      <c r="E940" t="inlineStr"/>
       <c r="F940" t="inlineStr"/>
-      <c r="G940" t="n">
-        <v>13</v>
-      </c>
+      <c r="G940" t="inlineStr"/>
       <c r="H940" t="inlineStr"/>
       <c r="I940" t="n">
         <v>3</v>
       </c>
       <c r="J940" t="inlineStr"/>
       <c r="K940" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L940" t="inlineStr"/>
-      <c r="M940" t="n">
-        <v>1</v>
-      </c>
+      <c r="M940" t="inlineStr"/>
       <c r="N940" t="inlineStr"/>
       <c r="O940" t="inlineStr"/>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>Jhanswa Kalan BO</t>
+          <t>Garhi BO</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>J7829</t>
+          <t>L5371</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Sahlawas SO</t>
+          <t>Sampla SO</t>
         </is>
       </c>
       <c r="D941" t="inlineStr"/>
@@ -30569,11 +30541,11 @@
       <c r="F941" t="inlineStr"/>
       <c r="G941" t="inlineStr"/>
       <c r="H941" t="inlineStr"/>
-      <c r="I941" t="inlineStr"/>
+      <c r="I941" t="n">
+        <v>3</v>
+      </c>
       <c r="J941" t="inlineStr"/>
-      <c r="K941" t="n">
-        <v>1</v>
-      </c>
+      <c r="K941" t="inlineStr"/>
       <c r="L941" t="inlineStr"/>
       <c r="M941" t="inlineStr"/>
       <c r="N941" t="inlineStr"/>
@@ -30582,30 +30554,24 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>Jnv Kiloi BO</t>
-        </is>
-      </c>
-      <c r="B942" t="inlineStr">
-        <is>
-          <t>N9279</t>
-        </is>
-      </c>
-      <c r="C942" t="inlineStr">
-        <is>
-          <t>Nehru College Jhajjar SO</t>
-        </is>
-      </c>
+          <t>Hassangarh SO</t>
+        </is>
+      </c>
+      <c r="B942" t="n">
+        <v>12440401</v>
+      </c>
+      <c r="C942" t="inlineStr"/>
       <c r="D942" t="inlineStr"/>
       <c r="E942" t="inlineStr"/>
       <c r="F942" t="inlineStr"/>
-      <c r="G942" t="n">
-        <v>10</v>
-      </c>
+      <c r="G942" t="inlineStr"/>
       <c r="H942" t="inlineStr"/>
-      <c r="I942" t="inlineStr"/>
+      <c r="I942" t="n">
+        <v>0</v>
+      </c>
       <c r="J942" t="inlineStr"/>
       <c r="K942" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L942" t="inlineStr"/>
       <c r="M942" t="inlineStr"/>
@@ -30615,29 +30581,29 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>Kablana BO</t>
+          <t>Kanheli BO</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>N9280</t>
+          <t>J7016</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Nehru College Jhajjar SO</t>
+          <t>Asthal Bohar SO</t>
         </is>
       </c>
       <c r="D943" t="inlineStr"/>
       <c r="E943" t="inlineStr"/>
       <c r="F943" t="inlineStr"/>
-      <c r="G943" t="inlineStr"/>
+      <c r="G943" t="n">
+        <v>1</v>
+      </c>
       <c r="H943" t="inlineStr"/>
       <c r="I943" t="inlineStr"/>
       <c r="J943" t="inlineStr"/>
-      <c r="K943" t="n">
-        <v>10</v>
-      </c>
+      <c r="K943" t="inlineStr"/>
       <c r="L943" t="inlineStr"/>
       <c r="M943" t="inlineStr"/>
       <c r="N943" t="inlineStr"/>
@@ -30646,17 +30612,17 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>Khatiwas BO</t>
+          <t>Karor BO</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>E6294</t>
+          <t>J7017</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>Jhajjar SO</t>
+          <t>Asthal Bohar SO</t>
         </is>
       </c>
       <c r="D944" t="inlineStr"/>
@@ -30664,11 +30630,11 @@
       <c r="F944" t="inlineStr"/>
       <c r="G944" t="inlineStr"/>
       <c r="H944" t="inlineStr"/>
-      <c r="I944" t="inlineStr"/>
+      <c r="I944" t="n">
+        <v>1</v>
+      </c>
       <c r="J944" t="inlineStr"/>
-      <c r="K944" t="n">
-        <v>1</v>
-      </c>
+      <c r="K944" t="inlineStr"/>
       <c r="L944" t="inlineStr"/>
       <c r="M944" t="inlineStr"/>
       <c r="N944" t="inlineStr"/>
@@ -30677,17 +30643,17 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>Kheri Asra BO</t>
+          <t>Kiloi BO</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>N9281</t>
+          <t>J7279</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Nehru College Jhajjar SO</t>
+          <t>Bhalaut SO</t>
         </is>
       </c>
       <c r="D945" t="inlineStr"/>
@@ -30695,11 +30661,11 @@
       <c r="F945" t="inlineStr"/>
       <c r="G945" t="inlineStr"/>
       <c r="H945" t="inlineStr"/>
-      <c r="I945" t="inlineStr"/>
+      <c r="I945" t="n">
+        <v>1</v>
+      </c>
       <c r="J945" t="inlineStr"/>
-      <c r="K945" t="n">
-        <v>1</v>
-      </c>
+      <c r="K945" t="inlineStr"/>
       <c r="L945" t="inlineStr"/>
       <c r="M945" t="inlineStr"/>
       <c r="N945" t="inlineStr"/>
@@ -30708,24 +30674,24 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>Khorra BO</t>
+          <t>Kulasi BO</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>G9345</t>
+          <t>N9649</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Bahu SO</t>
+          <t>Assaudha SO</t>
         </is>
       </c>
       <c r="D946" t="inlineStr"/>
       <c r="E946" t="inlineStr"/>
       <c r="F946" t="inlineStr"/>
       <c r="G946" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H946" t="inlineStr"/>
       <c r="I946" t="inlineStr"/>
@@ -30739,24 +30705,24 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>Lohari BO</t>
+          <t>Loharheri BO</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>A5091</t>
+          <t>L5376</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Machrauli SO</t>
+          <t>Sampla SO</t>
         </is>
       </c>
       <c r="D947" t="inlineStr"/>
       <c r="E947" t="inlineStr"/>
       <c r="F947" t="inlineStr"/>
       <c r="G947" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H947" t="inlineStr"/>
       <c r="I947" t="inlineStr"/>
@@ -30770,26 +30736,28 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>Machrauli SO</t>
-        </is>
-      </c>
-      <c r="B948" t="n">
-        <v>12410801</v>
-      </c>
-      <c r="C948" t="inlineStr"/>
+          <t>Luksar BO</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>L9906</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Bahadurgarh Mandi SO</t>
+        </is>
+      </c>
       <c r="D948" t="inlineStr"/>
       <c r="E948" t="inlineStr"/>
-      <c r="F948" t="n">
-        <v>0</v>
-      </c>
-      <c r="G948" t="n">
-        <v>4</v>
-      </c>
+      <c r="F948" t="inlineStr"/>
+      <c r="G948" t="inlineStr"/>
       <c r="H948" t="inlineStr"/>
       <c r="I948" t="inlineStr"/>
       <c r="J948" t="inlineStr"/>
       <c r="K948" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L948" t="inlineStr"/>
       <c r="M948" t="inlineStr"/>
@@ -30799,89 +30767,93 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>Madana Kalan BO</t>
-        </is>
-      </c>
-      <c r="B949" t="inlineStr">
-        <is>
-          <t>D7058</t>
-        </is>
-      </c>
-      <c r="C949" t="inlineStr">
-        <is>
-          <t>Dujana SO</t>
-        </is>
-      </c>
+          <t>Main Bazar Bahadurgarh  SO</t>
+        </is>
+      </c>
+      <c r="B949" t="n">
+        <v>12450705</v>
+      </c>
+      <c r="C949" t="inlineStr"/>
       <c r="D949" t="inlineStr"/>
       <c r="E949" t="inlineStr"/>
-      <c r="F949" t="inlineStr"/>
+      <c r="F949" t="n">
+        <v>1</v>
+      </c>
       <c r="G949" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H949" t="inlineStr"/>
-      <c r="I949" t="inlineStr"/>
+      <c r="I949" t="n">
+        <v>1</v>
+      </c>
       <c r="J949" t="inlineStr"/>
-      <c r="K949" t="inlineStr"/>
+      <c r="K949" t="n">
+        <v>8</v>
+      </c>
       <c r="L949" t="inlineStr"/>
       <c r="M949" t="inlineStr"/>
-      <c r="N949" t="inlineStr"/>
+      <c r="N949" t="n">
+        <v>1</v>
+      </c>
       <c r="O949" t="inlineStr"/>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>Mehem SO</t>
+          <t>Mandothi SO</t>
         </is>
       </c>
       <c r="B950" t="n">
-        <v>12411201</v>
+        <v>12450601</v>
       </c>
       <c r="C950" t="inlineStr"/>
       <c r="D950" t="inlineStr"/>
       <c r="E950" t="inlineStr"/>
-      <c r="F950" t="n">
-        <v>1</v>
-      </c>
-      <c r="G950" t="inlineStr"/>
+      <c r="F950" t="inlineStr"/>
+      <c r="G950" t="n">
+        <v>1</v>
+      </c>
       <c r="H950" t="inlineStr"/>
       <c r="I950" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J950" t="inlineStr"/>
       <c r="K950" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L950" t="inlineStr"/>
-      <c r="M950" t="n">
-        <v>1</v>
-      </c>
+      <c r="M950" t="inlineStr"/>
       <c r="N950" t="inlineStr"/>
       <c r="O950" t="inlineStr"/>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>Nehru College Jhajjar SO</t>
-        </is>
-      </c>
-      <c r="B951" t="n">
-        <v>12410401</v>
-      </c>
-      <c r="C951" t="inlineStr"/>
+          <t>Naya Bans BO</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>L5379</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Sampla SO</t>
+        </is>
+      </c>
       <c r="D951" t="inlineStr"/>
       <c r="E951" t="inlineStr"/>
-      <c r="F951" t="n">
-        <v>1</v>
-      </c>
+      <c r="F951" t="inlineStr"/>
       <c r="G951" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H951" t="inlineStr"/>
-      <c r="I951" t="inlineStr"/>
+      <c r="I951" t="n">
+        <v>1</v>
+      </c>
       <c r="J951" t="inlineStr"/>
-      <c r="K951" t="n">
-        <v>2</v>
-      </c>
+      <c r="K951" t="inlineStr"/>
       <c r="L951" t="inlineStr"/>
       <c r="M951" t="inlineStr"/>
       <c r="N951" t="inlineStr"/>
@@ -30890,28 +30862,30 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>Sahlawas SO</t>
-        </is>
-      </c>
-      <c r="B952" t="n">
-        <v>12414601</v>
-      </c>
-      <c r="C952" t="inlineStr"/>
+          <t>Paksma BO</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>J7283</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Bhalaut SO</t>
+        </is>
+      </c>
       <c r="D952" t="inlineStr"/>
       <c r="E952" t="inlineStr"/>
-      <c r="F952" t="n">
-        <v>1</v>
-      </c>
-      <c r="G952" t="n">
-        <v>2</v>
-      </c>
+      <c r="F952" t="inlineStr"/>
+      <c r="G952" t="inlineStr"/>
       <c r="H952" t="inlineStr"/>
       <c r="I952" t="n">
         <v>1</v>
       </c>
       <c r="J952" t="inlineStr"/>
       <c r="K952" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L952" t="inlineStr"/>
       <c r="M952" t="inlineStr"/>
@@ -30921,24 +30895,24 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>Subana BO</t>
+          <t>Rohad BO</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>J3755</t>
+          <t>L5380</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Dhakla SO</t>
+          <t>Sampla SO</t>
         </is>
       </c>
       <c r="D953" t="inlineStr"/>
       <c r="E953" t="inlineStr"/>
       <c r="F953" t="inlineStr"/>
       <c r="G953" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H953" t="inlineStr"/>
       <c r="I953" t="inlineStr"/>
@@ -30952,17 +30926,17 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>Sulodha BO</t>
+          <t>Samchana BO</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>E6295</t>
+          <t>H7487</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Jhajjar SO</t>
+          <t>Hassangarh SO</t>
         </is>
       </c>
       <c r="D954" t="inlineStr"/>
@@ -30971,7 +30945,7 @@
       <c r="G954" t="inlineStr"/>
       <c r="H954" t="inlineStr"/>
       <c r="I954" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J954" t="inlineStr"/>
       <c r="K954" t="inlineStr"/>
@@ -30983,29 +30957,27 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>Tumbaheri BO</t>
-        </is>
-      </c>
-      <c r="B955" t="inlineStr">
-        <is>
-          <t>J3757</t>
-        </is>
-      </c>
-      <c r="C955" t="inlineStr">
-        <is>
-          <t>Dhakla SO</t>
-        </is>
-      </c>
+          <t>Sampla SO</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>12450101</v>
+      </c>
+      <c r="C955" t="inlineStr"/>
       <c r="D955" t="inlineStr"/>
       <c r="E955" t="inlineStr"/>
       <c r="F955" t="inlineStr"/>
-      <c r="G955" t="inlineStr"/>
+      <c r="G955" t="n">
+        <v>8</v>
+      </c>
       <c r="H955" t="inlineStr"/>
       <c r="I955" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J955" t="inlineStr"/>
-      <c r="K955" t="inlineStr"/>
+      <c r="K955" t="n">
+        <v>1</v>
+      </c>
       <c r="L955" t="inlineStr"/>
       <c r="M955" t="inlineStr"/>
       <c r="N955" t="inlineStr"/>
@@ -31020,37 +30992,37 @@
       <c r="B956" t="inlineStr"/>
       <c r="C956" t="inlineStr"/>
       <c r="D956" t="n">
+        <v>1</v>
+      </c>
+      <c r="E956" t="n">
+        <v>0</v>
+      </c>
+      <c r="F956" t="n">
+        <v>1</v>
+      </c>
+      <c r="G956" t="n">
+        <v>68</v>
+      </c>
+      <c r="H956" t="n">
+        <v>0</v>
+      </c>
+      <c r="I956" t="n">
+        <v>17</v>
+      </c>
+      <c r="J956" t="n">
         <v>2</v>
       </c>
-      <c r="E956" t="n">
-        <v>1</v>
-      </c>
-      <c r="F956" t="n">
-        <v>10</v>
-      </c>
-      <c r="G956" t="n">
-        <v>55</v>
-      </c>
-      <c r="H956" t="n">
-        <v>0</v>
-      </c>
-      <c r="I956" t="n">
-        <v>12</v>
-      </c>
-      <c r="J956" t="n">
-        <v>1</v>
-      </c>
       <c r="K956" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="L956" t="n">
         <v>0</v>
       </c>
       <c r="M956" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N956" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O956" t="n">
         <v>0</v>
@@ -31159,25 +31131,27 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>Asthal Bohar SO</t>
+          <t>Bahu SO</t>
         </is>
       </c>
       <c r="B959" t="n">
-        <v>12402101</v>
+        <v>12414201</v>
       </c>
       <c r="C959" t="inlineStr"/>
       <c r="D959" t="inlineStr"/>
       <c r="E959" t="inlineStr"/>
       <c r="F959" t="inlineStr"/>
       <c r="G959" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H959" t="inlineStr"/>
       <c r="I959" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J959" t="inlineStr"/>
-      <c r="K959" t="inlineStr"/>
+      <c r="K959" t="n">
+        <v>1</v>
+      </c>
       <c r="L959" t="inlineStr"/>
       <c r="M959" t="inlineStr"/>
       <c r="N959" t="inlineStr"/>
@@ -31186,30 +31160,30 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>Bainsi BO</t>
-        </is>
-      </c>
-      <c r="B960" t="inlineStr">
-        <is>
-          <t>G2018</t>
-        </is>
-      </c>
-      <c r="C960" t="inlineStr">
-        <is>
-          <t>Nindana SO</t>
-        </is>
-      </c>
-      <c r="D960" t="inlineStr"/>
+          <t>Beri SO</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>12420101</v>
+      </c>
+      <c r="C960" t="inlineStr"/>
+      <c r="D960" t="n">
+        <v>1</v>
+      </c>
       <c r="E960" t="inlineStr"/>
-      <c r="F960" t="inlineStr"/>
-      <c r="G960" t="inlineStr"/>
+      <c r="F960" t="n">
+        <v>1</v>
+      </c>
+      <c r="G960" t="n">
+        <v>1</v>
+      </c>
       <c r="H960" t="inlineStr"/>
       <c r="I960" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J960" t="inlineStr"/>
       <c r="K960" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L960" t="inlineStr"/>
       <c r="M960" t="inlineStr"/>
@@ -31219,28 +31193,30 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>Baland BO</t>
+          <t>Birdhana BO</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>O0155</t>
+          <t>D7057</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Police Training Center Sunaria SO</t>
+          <t>Dujana SO</t>
         </is>
       </c>
       <c r="D961" t="inlineStr"/>
       <c r="E961" t="inlineStr"/>
-      <c r="F961" t="inlineStr"/>
+      <c r="F961" t="n">
+        <v>1</v>
+      </c>
       <c r="G961" t="inlineStr"/>
       <c r="H961" t="inlineStr"/>
       <c r="I961" t="inlineStr"/>
       <c r="J961" t="inlineStr"/>
       <c r="K961" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L961" t="inlineStr"/>
       <c r="M961" t="inlineStr"/>
@@ -31250,20 +31226,26 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>Bhalaut SO</t>
-        </is>
-      </c>
-      <c r="B962" t="n">
-        <v>12440101</v>
-      </c>
-      <c r="C962" t="inlineStr"/>
+          <t>Bishan BO</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>A3311</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Beri SO</t>
+        </is>
+      </c>
       <c r="D962" t="inlineStr"/>
       <c r="E962" t="inlineStr"/>
       <c r="F962" t="inlineStr"/>
       <c r="G962" t="inlineStr"/>
       <c r="H962" t="inlineStr"/>
       <c r="I962" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J962" t="inlineStr"/>
       <c r="K962" t="n">
@@ -31277,29 +31259,33 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>Bhali Anandpur BO</t>
+          <t>Chhappar BO</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>O0156</t>
+          <t>B3544</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Police Training Center Sunaria SO</t>
+          <t>Machrauli SO</t>
         </is>
       </c>
       <c r="D963" t="inlineStr"/>
       <c r="E963" t="inlineStr"/>
       <c r="F963" t="n">
-        <v>2</v>
-      </c>
-      <c r="G963" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G963" t="n">
+        <v>1</v>
+      </c>
       <c r="H963" t="inlineStr"/>
       <c r="I963" t="inlineStr"/>
       <c r="J963" t="inlineStr"/>
-      <c r="K963" t="inlineStr"/>
+      <c r="K963" t="n">
+        <v>6</v>
+      </c>
       <c r="L963" t="inlineStr"/>
       <c r="M963" t="inlineStr"/>
       <c r="N963" t="inlineStr"/>
@@ -31308,19 +31294,13 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>Chamaria BO</t>
-        </is>
-      </c>
-      <c r="B964" t="inlineStr">
-        <is>
-          <t>H9417</t>
-        </is>
-      </c>
-      <c r="C964" t="inlineStr">
-        <is>
-          <t>Sanghi SO</t>
-        </is>
-      </c>
+          <t>Court Complex Jhajjar SO</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>12410301</v>
+      </c>
+      <c r="C964" t="inlineStr"/>
       <c r="D964" t="inlineStr"/>
       <c r="E964" t="inlineStr"/>
       <c r="F964" t="inlineStr"/>
@@ -31330,7 +31310,9 @@
         <v>1</v>
       </c>
       <c r="J964" t="inlineStr"/>
-      <c r="K964" t="inlineStr"/>
+      <c r="K964" t="n">
+        <v>1</v>
+      </c>
       <c r="L964" t="inlineStr"/>
       <c r="M964" t="inlineStr"/>
       <c r="N964" t="inlineStr"/>
@@ -31339,17 +31321,17 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>Chandi BO</t>
+          <t>Darauli BO</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>F3581</t>
+          <t>J3750</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Lakhan Majra SO</t>
+          <t>Dhakla SO</t>
         </is>
       </c>
       <c r="D965" t="inlineStr"/>
@@ -31370,28 +31352,26 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>Dobh BO</t>
-        </is>
-      </c>
-      <c r="B966" t="inlineStr">
-        <is>
-          <t>O0157</t>
-        </is>
-      </c>
-      <c r="C966" t="inlineStr">
-        <is>
-          <t>Police Training Center Sunaria SO</t>
-        </is>
-      </c>
+          <t>Dhakla SO</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>12410901</v>
+      </c>
+      <c r="C966" t="inlineStr"/>
       <c r="D966" t="inlineStr"/>
       <c r="E966" t="inlineStr"/>
       <c r="F966" t="inlineStr"/>
-      <c r="G966" t="inlineStr"/>
+      <c r="G966" t="n">
+        <v>1</v>
+      </c>
       <c r="H966" t="inlineStr"/>
       <c r="I966" t="n">
-        <v>1</v>
-      </c>
-      <c r="J966" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J966" t="n">
+        <v>1</v>
+      </c>
       <c r="K966" t="inlineStr"/>
       <c r="L966" t="inlineStr"/>
       <c r="M966" t="inlineStr"/>
@@ -31401,28 +31381,26 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>Gaddi Kheri BO</t>
-        </is>
-      </c>
-      <c r="B967" t="inlineStr">
-        <is>
-          <t>O0158</t>
-        </is>
-      </c>
-      <c r="C967" t="inlineStr">
-        <is>
-          <t>Police Training Center Sunaria SO</t>
-        </is>
-      </c>
+          <t>Dighal SO</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>12410701</v>
+      </c>
+      <c r="C967" t="inlineStr"/>
       <c r="D967" t="inlineStr"/>
       <c r="E967" t="inlineStr"/>
       <c r="F967" t="inlineStr"/>
-      <c r="G967" t="inlineStr"/>
+      <c r="G967" t="n">
+        <v>1</v>
+      </c>
       <c r="H967" t="inlineStr"/>
-      <c r="I967" t="inlineStr"/>
+      <c r="I967" t="n">
+        <v>1</v>
+      </c>
       <c r="J967" t="inlineStr"/>
       <c r="K967" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L967" t="inlineStr"/>
       <c r="M967" t="inlineStr"/>
@@ -31432,24 +31410,26 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>Gandhi Camp SO</t>
+          <t>Dubaldhan SO</t>
         </is>
       </c>
       <c r="B968" t="n">
-        <v>12400102</v>
+        <v>12420201</v>
       </c>
       <c r="C968" t="inlineStr"/>
       <c r="D968" t="inlineStr"/>
       <c r="E968" t="inlineStr"/>
       <c r="F968" t="inlineStr"/>
-      <c r="G968" t="inlineStr"/>
+      <c r="G968" t="n">
+        <v>3</v>
+      </c>
       <c r="H968" t="inlineStr"/>
       <c r="I968" t="n">
         <v>1</v>
       </c>
       <c r="J968" t="inlineStr"/>
       <c r="K968" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L968" t="inlineStr"/>
       <c r="M968" t="inlineStr"/>
@@ -31459,29 +31439,27 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>Ghillaur Kalan BO</t>
-        </is>
-      </c>
-      <c r="B969" t="inlineStr">
-        <is>
-          <t>H9418</t>
-        </is>
-      </c>
-      <c r="C969" t="inlineStr">
-        <is>
-          <t>Sanghi SO</t>
-        </is>
-      </c>
+          <t>Dujana SO</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>12410201</v>
+      </c>
+      <c r="C969" t="inlineStr"/>
       <c r="D969" t="inlineStr"/>
       <c r="E969" t="inlineStr"/>
-      <c r="F969" t="inlineStr"/>
-      <c r="G969" t="inlineStr"/>
+      <c r="F969" t="n">
+        <v>0</v>
+      </c>
+      <c r="G969" t="n">
+        <v>0</v>
+      </c>
       <c r="H969" t="inlineStr"/>
-      <c r="I969" t="n">
-        <v>3</v>
-      </c>
+      <c r="I969" t="inlineStr"/>
       <c r="J969" t="inlineStr"/>
-      <c r="K969" t="inlineStr"/>
+      <c r="K969" t="n">
+        <v>2</v>
+      </c>
       <c r="L969" t="inlineStr"/>
       <c r="M969" t="inlineStr"/>
       <c r="N969" t="inlineStr"/>
@@ -31490,17 +31468,17 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>Girawar BO</t>
+          <t>Jahangirpur BO</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>H8969</t>
+          <t>N9278</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Madina SO</t>
+          <t>Nehru College Jhajjar SO</t>
         </is>
       </c>
       <c r="D970" t="inlineStr"/>
@@ -31511,7 +31489,7 @@
       <c r="I970" t="inlineStr"/>
       <c r="J970" t="inlineStr"/>
       <c r="K970" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="L970" t="inlineStr"/>
       <c r="M970" t="inlineStr"/>
@@ -31521,44 +31499,52 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>Janta Colony Rohtak SO</t>
+          <t>Jhajjar SO</t>
         </is>
       </c>
       <c r="B971" t="n">
-        <v>12400104</v>
+        <v>12410302</v>
       </c>
       <c r="C971" t="inlineStr"/>
-      <c r="D971" t="inlineStr"/>
-      <c r="E971" t="inlineStr"/>
+      <c r="D971" t="n">
+        <v>1</v>
+      </c>
+      <c r="E971" t="n">
+        <v>1</v>
+      </c>
       <c r="F971" t="inlineStr"/>
       <c r="G971" t="n">
+        <v>13</v>
+      </c>
+      <c r="H971" t="inlineStr"/>
+      <c r="I971" t="n">
         <v>3</v>
       </c>
-      <c r="H971" t="inlineStr"/>
-      <c r="I971" t="inlineStr"/>
       <c r="J971" t="inlineStr"/>
       <c r="K971" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L971" t="inlineStr"/>
-      <c r="M971" t="inlineStr"/>
+      <c r="M971" t="n">
+        <v>1</v>
+      </c>
       <c r="N971" t="inlineStr"/>
       <c r="O971" t="inlineStr"/>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>Jassia BO</t>
+          <t>Jhanswa Kalan BO</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>H9419</t>
+          <t>J7829</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>Sanghi SO</t>
+          <t>Sahlawas SO</t>
         </is>
       </c>
       <c r="D972" t="inlineStr"/>
@@ -31566,11 +31552,11 @@
       <c r="F972" t="inlineStr"/>
       <c r="G972" t="inlineStr"/>
       <c r="H972" t="inlineStr"/>
-      <c r="I972" t="n">
-        <v>3</v>
-      </c>
+      <c r="I972" t="inlineStr"/>
       <c r="J972" t="inlineStr"/>
-      <c r="K972" t="inlineStr"/>
+      <c r="K972" t="n">
+        <v>1</v>
+      </c>
       <c r="L972" t="inlineStr"/>
       <c r="M972" t="inlineStr"/>
       <c r="N972" t="inlineStr"/>
@@ -31579,27 +31565,27 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>Jindran BO</t>
+          <t>Jnv Kiloi BO</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>H9420</t>
+          <t>N9279</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Sanghi SO</t>
+          <t>Nehru College Jhajjar SO</t>
         </is>
       </c>
       <c r="D973" t="inlineStr"/>
       <c r="E973" t="inlineStr"/>
       <c r="F973" t="inlineStr"/>
-      <c r="G973" t="inlineStr"/>
+      <c r="G973" t="n">
+        <v>10</v>
+      </c>
       <c r="H973" t="inlineStr"/>
-      <c r="I973" t="n">
-        <v>2</v>
-      </c>
+      <c r="I973" t="inlineStr"/>
       <c r="J973" t="inlineStr"/>
       <c r="K973" t="n">
         <v>1</v>
@@ -31612,24 +31598,28 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>Kahnaur SO</t>
-        </is>
-      </c>
-      <c r="B974" t="n">
-        <v>12441201</v>
-      </c>
-      <c r="C974" t="inlineStr"/>
+          <t>Kablana BO</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>N9280</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Nehru College Jhajjar SO</t>
+        </is>
+      </c>
       <c r="D974" t="inlineStr"/>
       <c r="E974" t="inlineStr"/>
       <c r="F974" t="inlineStr"/>
       <c r="G974" t="inlineStr"/>
       <c r="H974" t="inlineStr"/>
-      <c r="I974" t="n">
-        <v>2</v>
-      </c>
+      <c r="I974" t="inlineStr"/>
       <c r="J974" t="inlineStr"/>
       <c r="K974" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L974" t="inlineStr"/>
       <c r="M974" t="inlineStr"/>
@@ -31639,17 +31629,17 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>Kahri BO</t>
+          <t>Khatiwas BO</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>B3545</t>
+          <t>E6294</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Machrauli SO</t>
+          <t>Jhajjar SO</t>
         </is>
       </c>
       <c r="D975" t="inlineStr"/>
@@ -31670,25 +31660,29 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>Kalanaur SO Rohtak</t>
-        </is>
-      </c>
-      <c r="B976" t="n">
-        <v>12411301</v>
-      </c>
-      <c r="C976" t="inlineStr"/>
+          <t>Kheri Asra BO</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>N9281</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Nehru College Jhajjar SO</t>
+        </is>
+      </c>
       <c r="D976" t="inlineStr"/>
       <c r="E976" t="inlineStr"/>
       <c r="F976" t="inlineStr"/>
-      <c r="G976" t="n">
-        <v>0</v>
-      </c>
+      <c r="G976" t="inlineStr"/>
       <c r="H976" t="inlineStr"/>
-      <c r="I976" t="n">
-        <v>1</v>
-      </c>
+      <c r="I976" t="inlineStr"/>
       <c r="J976" t="inlineStr"/>
-      <c r="K976" t="inlineStr"/>
+      <c r="K976" t="n">
+        <v>1</v>
+      </c>
       <c r="L976" t="inlineStr"/>
       <c r="M976" t="inlineStr"/>
       <c r="N976" t="inlineStr"/>
@@ -31697,27 +31691,29 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>Kansala SO</t>
-        </is>
-      </c>
-      <c r="B977" t="n">
-        <v>12440601</v>
-      </c>
-      <c r="C977" t="inlineStr"/>
+          <t>Khorra BO</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>G9345</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Bahu SO</t>
+        </is>
+      </c>
       <c r="D977" t="inlineStr"/>
       <c r="E977" t="inlineStr"/>
       <c r="F977" t="inlineStr"/>
       <c r="G977" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H977" t="inlineStr"/>
-      <c r="I977" t="n">
-        <v>1</v>
-      </c>
+      <c r="I977" t="inlineStr"/>
       <c r="J977" t="inlineStr"/>
-      <c r="K977" t="n">
-        <v>1</v>
-      </c>
+      <c r="K977" t="inlineStr"/>
       <c r="L977" t="inlineStr"/>
       <c r="M977" t="inlineStr"/>
       <c r="N977" t="inlineStr"/>
@@ -31726,29 +31722,27 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>Karontha BO</t>
+          <t>Lohari BO</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>O0159</t>
+          <t>A5091</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Police Training Center Sunaria SO</t>
+          <t>Machrauli SO</t>
         </is>
       </c>
       <c r="D978" t="inlineStr"/>
       <c r="E978" t="inlineStr"/>
-      <c r="F978" t="n">
-        <v>1</v>
-      </c>
-      <c r="G978" t="inlineStr"/>
+      <c r="F978" t="inlineStr"/>
+      <c r="G978" t="n">
+        <v>5</v>
+      </c>
       <c r="H978" t="inlineStr"/>
-      <c r="I978" t="n">
-        <v>1</v>
-      </c>
+      <c r="I978" t="inlineStr"/>
       <c r="J978" t="inlineStr"/>
       <c r="K978" t="inlineStr"/>
       <c r="L978" t="inlineStr"/>
@@ -31759,29 +31753,27 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>Khairari BO</t>
-        </is>
-      </c>
-      <c r="B979" t="inlineStr">
-        <is>
-          <t>J2619</t>
-        </is>
-      </c>
-      <c r="C979" t="inlineStr">
-        <is>
-          <t>Kalanaur SO Rohtak</t>
-        </is>
-      </c>
+          <t>Machrauli SO</t>
+        </is>
+      </c>
+      <c r="B979" t="n">
+        <v>12410801</v>
+      </c>
+      <c r="C979" t="inlineStr"/>
       <c r="D979" t="inlineStr"/>
       <c r="E979" t="inlineStr"/>
-      <c r="F979" t="inlineStr"/>
+      <c r="F979" t="n">
+        <v>0</v>
+      </c>
       <c r="G979" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H979" t="inlineStr"/>
       <c r="I979" t="inlineStr"/>
       <c r="J979" t="inlineStr"/>
-      <c r="K979" t="inlineStr"/>
+      <c r="K979" t="n">
+        <v>1</v>
+      </c>
       <c r="L979" t="inlineStr"/>
       <c r="M979" t="inlineStr"/>
       <c r="N979" t="inlineStr"/>
@@ -31790,29 +31782,29 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>Khidwali BO</t>
+          <t>Madana Kalan BO</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>H9422</t>
+          <t>D7058</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Sanghi SO</t>
+          <t>Dujana SO</t>
         </is>
       </c>
       <c r="D980" t="inlineStr"/>
       <c r="E980" t="inlineStr"/>
       <c r="F980" t="inlineStr"/>
-      <c r="G980" t="inlineStr"/>
+      <c r="G980" t="n">
+        <v>3</v>
+      </c>
       <c r="H980" t="inlineStr"/>
       <c r="I980" t="inlineStr"/>
       <c r="J980" t="inlineStr"/>
-      <c r="K980" t="n">
-        <v>1</v>
-      </c>
+      <c r="K980" t="inlineStr"/>
       <c r="L980" t="inlineStr"/>
       <c r="M980" t="inlineStr"/>
       <c r="N980" t="inlineStr"/>
@@ -31821,53 +31813,57 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>Lakhan Majra SO</t>
+          <t>Mehem SO</t>
         </is>
       </c>
       <c r="B981" t="n">
-        <v>12451401</v>
+        <v>12411201</v>
       </c>
       <c r="C981" t="inlineStr"/>
       <c r="D981" t="inlineStr"/>
       <c r="E981" t="inlineStr"/>
-      <c r="F981" t="inlineStr"/>
-      <c r="G981" t="n">
-        <v>0</v>
-      </c>
+      <c r="F981" t="n">
+        <v>1</v>
+      </c>
+      <c r="G981" t="inlineStr"/>
       <c r="H981" t="inlineStr"/>
       <c r="I981" t="n">
         <v>1</v>
       </c>
       <c r="J981" t="inlineStr"/>
       <c r="K981" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L981" t="inlineStr"/>
-      <c r="M981" t="inlineStr"/>
+      <c r="M981" t="n">
+        <v>1</v>
+      </c>
       <c r="N981" t="inlineStr"/>
       <c r="O981" t="inlineStr"/>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>Madina SO</t>
+          <t>Nehru College Jhajjar SO</t>
         </is>
       </c>
       <c r="B982" t="n">
-        <v>12411101</v>
+        <v>12410401</v>
       </c>
       <c r="C982" t="inlineStr"/>
       <c r="D982" t="inlineStr"/>
       <c r="E982" t="inlineStr"/>
-      <c r="F982" t="inlineStr"/>
+      <c r="F982" t="n">
+        <v>1</v>
+      </c>
       <c r="G982" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H982" t="inlineStr"/>
       <c r="I982" t="inlineStr"/>
       <c r="J982" t="inlineStr"/>
       <c r="K982" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L982" t="inlineStr"/>
       <c r="M982" t="inlineStr"/>
@@ -31877,47 +31873,55 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>Model Town SO Rohtak</t>
+          <t>Sahlawas SO</t>
         </is>
       </c>
       <c r="B983" t="n">
-        <v>12400107</v>
+        <v>12414601</v>
       </c>
       <c r="C983" t="inlineStr"/>
       <c r="D983" t="inlineStr"/>
       <c r="E983" t="inlineStr"/>
-      <c r="F983" t="inlineStr"/>
+      <c r="F983" t="n">
+        <v>1</v>
+      </c>
       <c r="G983" t="n">
         <v>2</v>
       </c>
       <c r="H983" t="inlineStr"/>
-      <c r="I983" t="inlineStr"/>
+      <c r="I983" t="n">
+        <v>1</v>
+      </c>
       <c r="J983" t="inlineStr"/>
       <c r="K983" t="n">
         <v>3</v>
       </c>
       <c r="L983" t="inlineStr"/>
       <c r="M983" t="inlineStr"/>
-      <c r="N983" t="n">
-        <v>3</v>
-      </c>
+      <c r="N983" t="inlineStr"/>
       <c r="O983" t="inlineStr"/>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>Mokhra SO</t>
-        </is>
-      </c>
-      <c r="B984" t="n">
-        <v>12402201</v>
-      </c>
-      <c r="C984" t="inlineStr"/>
+          <t>Subana BO</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>J3755</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Dhakla SO</t>
+        </is>
+      </c>
       <c r="D984" t="inlineStr"/>
       <c r="E984" t="inlineStr"/>
       <c r="F984" t="inlineStr"/>
       <c r="G984" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H984" t="inlineStr"/>
       <c r="I984" t="inlineStr"/>
@@ -31931,25 +31935,29 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>Nindana SO</t>
-        </is>
-      </c>
-      <c r="B985" t="n">
-        <v>12451301</v>
-      </c>
-      <c r="C985" t="inlineStr"/>
+          <t>Sulodha BO</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>E6295</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Jhajjar SO</t>
+        </is>
+      </c>
       <c r="D985" t="inlineStr"/>
       <c r="E985" t="inlineStr"/>
       <c r="F985" t="inlineStr"/>
       <c r="G985" t="inlineStr"/>
       <c r="H985" t="inlineStr"/>
       <c r="I985" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J985" t="inlineStr"/>
-      <c r="K985" t="n">
-        <v>0</v>
-      </c>
+      <c r="K985" t="inlineStr"/>
       <c r="L985" t="inlineStr"/>
       <c r="M985" t="inlineStr"/>
       <c r="N985" t="inlineStr"/>
@@ -31958,27 +31966,29 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>Police Training Center Sunaria SO</t>
-        </is>
-      </c>
-      <c r="B986" t="n">
-        <v>12401001</v>
-      </c>
-      <c r="C986" t="inlineStr"/>
+          <t>Tumbaheri BO</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>J3757</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Dhakla SO</t>
+        </is>
+      </c>
       <c r="D986" t="inlineStr"/>
       <c r="E986" t="inlineStr"/>
-      <c r="F986" t="n">
-        <v>0</v>
-      </c>
+      <c r="F986" t="inlineStr"/>
       <c r="G986" t="inlineStr"/>
       <c r="H986" t="inlineStr"/>
       <c r="I986" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J986" t="inlineStr"/>
-      <c r="K986" t="n">
-        <v>0</v>
-      </c>
+      <c r="K986" t="inlineStr"/>
       <c r="L986" t="inlineStr"/>
       <c r="M986" t="inlineStr"/>
       <c r="N986" t="inlineStr"/>
@@ -31987,62 +31997,64 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>Rohtak HO</t>
-        </is>
-      </c>
-      <c r="B987" t="n">
-        <v>12400100</v>
-      </c>
+          <t>Total:</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr"/>
       <c r="C987" t="inlineStr"/>
-      <c r="D987" t="inlineStr"/>
-      <c r="E987" t="inlineStr"/>
+      <c r="D987" t="n">
+        <v>2</v>
+      </c>
+      <c r="E987" t="n">
+        <v>1</v>
+      </c>
       <c r="F987" t="n">
+        <v>10</v>
+      </c>
+      <c r="G987" t="n">
+        <v>55</v>
+      </c>
+      <c r="H987" t="n">
+        <v>0</v>
+      </c>
+      <c r="I987" t="n">
+        <v>12</v>
+      </c>
+      <c r="J987" t="n">
+        <v>1</v>
+      </c>
+      <c r="K987" t="n">
+        <v>63</v>
+      </c>
+      <c r="L987" t="n">
+        <v>0</v>
+      </c>
+      <c r="M987" t="n">
         <v>2</v>
       </c>
-      <c r="G987" t="n">
-        <v>3</v>
-      </c>
-      <c r="H987" t="inlineStr"/>
-      <c r="I987" t="n">
-        <v>1</v>
-      </c>
-      <c r="J987" t="n">
-        <v>1</v>
-      </c>
-      <c r="K987" t="n">
-        <v>11</v>
-      </c>
-      <c r="L987" t="inlineStr"/>
-      <c r="M987" t="inlineStr"/>
-      <c r="N987" t="inlineStr"/>
-      <c r="O987" t="inlineStr"/>
+      <c r="N987" t="n">
+        <v>0</v>
+      </c>
+      <c r="O987" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>Sampel BO</t>
-        </is>
-      </c>
-      <c r="B988" t="inlineStr">
-        <is>
-          <t>J2621</t>
-        </is>
-      </c>
-      <c r="C988" t="inlineStr">
-        <is>
-          <t>Kalanaur SO Rohtak</t>
-        </is>
-      </c>
+          <t xml:space="preserve">
+Product Wise A/C Report
+</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr"/>
+      <c r="C988" t="inlineStr"/>
       <c r="D988" t="inlineStr"/>
       <c r="E988" t="inlineStr"/>
       <c r="F988" t="inlineStr"/>
-      <c r="G988" t="n">
-        <v>6</v>
-      </c>
+      <c r="G988" t="inlineStr"/>
       <c r="H988" t="inlineStr"/>
-      <c r="I988" t="n">
-        <v>1</v>
-      </c>
+      <c r="I988" t="inlineStr"/>
       <c r="J988" t="inlineStr"/>
       <c r="K988" t="inlineStr"/>
       <c r="L988" t="inlineStr"/>
@@ -32053,56 +32065,100 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>Sanghi SO</t>
-        </is>
-      </c>
-      <c r="B989" t="n">
-        <v>12430301</v>
-      </c>
-      <c r="C989" t="inlineStr"/>
-      <c r="D989" t="inlineStr"/>
-      <c r="E989" t="n">
-        <v>1</v>
-      </c>
-      <c r="F989" t="inlineStr"/>
-      <c r="G989" t="inlineStr"/>
-      <c r="H989" t="inlineStr"/>
-      <c r="I989" t="n">
-        <v>0</v>
-      </c>
-      <c r="J989" t="inlineStr"/>
-      <c r="K989" t="n">
-        <v>0</v>
-      </c>
-      <c r="L989" t="inlineStr"/>
-      <c r="M989" t="inlineStr"/>
-      <c r="N989" t="inlineStr"/>
-      <c r="O989" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>SOL ID / BOCODE</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>SO Name</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>MIS</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>PPFGP</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>SBBAS</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>SBSGP</t>
+        </is>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>SCSS</t>
+        </is>
+      </c>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>PRFTS</t>
+        </is>
+      </c>
+      <c r="M989" t="inlineStr">
+        <is>
+          <t>KVN</t>
+        </is>
+      </c>
+      <c r="N989" t="inlineStr">
+        <is>
+          <t>NSC8</t>
+        </is>
+      </c>
+      <c r="O989" t="inlineStr">
+        <is>
+          <t>MSSC</t>
+        </is>
+      </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>Singhpura Kalan BO</t>
-        </is>
-      </c>
-      <c r="B990" t="inlineStr">
-        <is>
-          <t>C8462</t>
-        </is>
-      </c>
-      <c r="C990" t="inlineStr">
-        <is>
-          <t>Lakhan Majra SO</t>
-        </is>
-      </c>
+          <t>Asthal Bohar SO</t>
+        </is>
+      </c>
+      <c r="B990" t="n">
+        <v>12402101</v>
+      </c>
+      <c r="C990" t="inlineStr"/>
       <c r="D990" t="inlineStr"/>
       <c r="E990" t="inlineStr"/>
       <c r="F990" t="inlineStr"/>
       <c r="G990" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H990" t="inlineStr"/>
-      <c r="I990" t="inlineStr"/>
+      <c r="I990" t="n">
+        <v>0</v>
+      </c>
       <c r="J990" t="inlineStr"/>
       <c r="K990" t="inlineStr"/>
       <c r="L990" t="inlineStr"/>
@@ -32113,17 +32169,17 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>Sisarkhas BO</t>
+          <t>Bainsi BO</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>J9571</t>
+          <t>G2018</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Mehem SO</t>
+          <t>Nindana SO</t>
         </is>
       </c>
       <c r="D991" t="inlineStr"/>
@@ -32131,10 +32187,12 @@
       <c r="F991" t="inlineStr"/>
       <c r="G991" t="inlineStr"/>
       <c r="H991" t="inlineStr"/>
-      <c r="I991" t="inlineStr"/>
+      <c r="I991" t="n">
+        <v>1</v>
+      </c>
       <c r="J991" t="inlineStr"/>
       <c r="K991" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L991" t="inlineStr"/>
       <c r="M991" t="inlineStr"/>
@@ -32144,17 +32202,17 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>Sundana BO</t>
+          <t>Baland BO</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>J8919</t>
+          <t>O0155</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>Kahnaur SO</t>
+          <t>Police Training Center Sunaria SO</t>
         </is>
       </c>
       <c r="D992" t="inlineStr"/>
@@ -32165,7 +32223,7 @@
       <c r="I992" t="inlineStr"/>
       <c r="J992" t="inlineStr"/>
       <c r="K992" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L992" t="inlineStr"/>
       <c r="M992" t="inlineStr"/>
@@ -32175,61 +32233,51 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>Total:</t>
-        </is>
-      </c>
-      <c r="B993" t="inlineStr"/>
+          <t>Bhalaut SO</t>
+        </is>
+      </c>
+      <c r="B993" t="n">
+        <v>12440101</v>
+      </c>
       <c r="C993" t="inlineStr"/>
-      <c r="D993" t="n">
-        <v>0</v>
-      </c>
-      <c r="E993" t="n">
-        <v>0</v>
-      </c>
-      <c r="F993" t="n">
-        <v>3</v>
-      </c>
-      <c r="G993" t="n">
-        <v>16</v>
-      </c>
-      <c r="H993" t="n">
-        <v>0</v>
-      </c>
+      <c r="D993" t="inlineStr"/>
+      <c r="E993" t="inlineStr"/>
+      <c r="F993" t="inlineStr"/>
+      <c r="G993" t="inlineStr"/>
+      <c r="H993" t="inlineStr"/>
       <c r="I993" t="n">
-        <v>19</v>
-      </c>
-      <c r="J993" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J993" t="inlineStr"/>
       <c r="K993" t="n">
-        <v>76</v>
-      </c>
-      <c r="L993" t="n">
-        <v>0</v>
-      </c>
-      <c r="M993" t="n">
-        <v>0</v>
-      </c>
-      <c r="N993" t="n">
-        <v>3</v>
-      </c>
-      <c r="O993" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L993" t="inlineStr"/>
+      <c r="M993" t="inlineStr"/>
+      <c r="N993" t="inlineStr"/>
+      <c r="O993" t="inlineStr"/>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Product Wise A/C Report
-</t>
-        </is>
-      </c>
-      <c r="B994" t="inlineStr"/>
-      <c r="C994" t="inlineStr"/>
+          <t>Bhali Anandpur BO</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>O0156</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Police Training Center Sunaria SO</t>
+        </is>
+      </c>
       <c r="D994" t="inlineStr"/>
       <c r="E994" t="inlineStr"/>
-      <c r="F994" t="inlineStr"/>
+      <c r="F994" t="n">
+        <v>2</v>
+      </c>
       <c r="G994" t="inlineStr"/>
       <c r="H994" t="inlineStr"/>
       <c r="I994" t="inlineStr"/>
@@ -32243,94 +32291,48 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Chamaria BO</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>SOL ID / BOCODE</t>
+          <t>H9417</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>SO Name</t>
-        </is>
-      </c>
-      <c r="D995" t="inlineStr">
-        <is>
-          <t>MIS</t>
-        </is>
-      </c>
-      <c r="E995" t="inlineStr">
-        <is>
-          <t>PPFGP</t>
-        </is>
-      </c>
-      <c r="F995" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="G995" t="inlineStr">
-        <is>
-          <t>RD</t>
-        </is>
-      </c>
-      <c r="H995" t="inlineStr">
-        <is>
-          <t>SBBAS</t>
-        </is>
-      </c>
-      <c r="I995" t="inlineStr">
-        <is>
-          <t>SBSGP</t>
-        </is>
-      </c>
-      <c r="J995" t="inlineStr">
-        <is>
-          <t>SCSS</t>
-        </is>
-      </c>
-      <c r="K995" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="L995" t="inlineStr">
-        <is>
-          <t>PRFTS</t>
-        </is>
-      </c>
-      <c r="M995" t="inlineStr">
-        <is>
-          <t>KVN</t>
-        </is>
-      </c>
-      <c r="N995" t="inlineStr">
-        <is>
-          <t>NSC8</t>
-        </is>
-      </c>
-      <c r="O995" t="inlineStr">
-        <is>
-          <t>MSSC</t>
-        </is>
-      </c>
+          <t>Sanghi SO</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr"/>
+      <c r="E995" t="inlineStr"/>
+      <c r="F995" t="inlineStr"/>
+      <c r="G995" t="inlineStr"/>
+      <c r="H995" t="inlineStr"/>
+      <c r="I995" t="n">
+        <v>1</v>
+      </c>
+      <c r="J995" t="inlineStr"/>
+      <c r="K995" t="inlineStr"/>
+      <c r="L995" t="inlineStr"/>
+      <c r="M995" t="inlineStr"/>
+      <c r="N995" t="inlineStr"/>
+      <c r="O995" t="inlineStr"/>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>AhulanaGohana BO</t>
+          <t>Chandi BO</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>L4458</t>
+          <t>F3581</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Gohana SO</t>
+          <t>Lakhan Majra SO</t>
         </is>
       </c>
       <c r="D996" t="inlineStr"/>
@@ -32351,17 +32353,17 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>Barona BO</t>
+          <t>Dobh BO</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>J9551</t>
+          <t>O0157</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>Kharkhauda SO</t>
+          <t>Police Training Center Sunaria SO</t>
         </is>
       </c>
       <c r="D997" t="inlineStr"/>
@@ -32369,11 +32371,11 @@
       <c r="F997" t="inlineStr"/>
       <c r="G997" t="inlineStr"/>
       <c r="H997" t="inlineStr"/>
-      <c r="I997" t="inlineStr"/>
+      <c r="I997" t="n">
+        <v>1</v>
+      </c>
       <c r="J997" t="inlineStr"/>
-      <c r="K997" t="n">
-        <v>23</v>
-      </c>
+      <c r="K997" t="inlineStr"/>
       <c r="L997" t="inlineStr"/>
       <c r="M997" t="inlineStr"/>
       <c r="N997" t="inlineStr"/>
@@ -32382,29 +32384,29 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>Busana BO</t>
+          <t>Gaddi Kheri BO</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>L6252</t>
+          <t>O0158</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Mundlana SO</t>
+          <t>Police Training Center Sunaria SO</t>
         </is>
       </c>
       <c r="D998" t="inlineStr"/>
       <c r="E998" t="inlineStr"/>
       <c r="F998" t="inlineStr"/>
-      <c r="G998" t="n">
-        <v>5</v>
-      </c>
+      <c r="G998" t="inlineStr"/>
       <c r="H998" t="inlineStr"/>
       <c r="I998" t="inlineStr"/>
       <c r="J998" t="inlineStr"/>
-      <c r="K998" t="inlineStr"/>
+      <c r="K998" t="n">
+        <v>6</v>
+      </c>
       <c r="L998" t="inlineStr"/>
       <c r="M998" t="inlineStr"/>
       <c r="N998" t="inlineStr"/>
@@ -32413,23 +32415,25 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>Butana SO</t>
+          <t>Gandhi Camp SO</t>
         </is>
       </c>
       <c r="B999" t="n">
-        <v>13130201</v>
+        <v>12400102</v>
       </c>
       <c r="C999" t="inlineStr"/>
       <c r="D999" t="inlineStr"/>
       <c r="E999" t="inlineStr"/>
       <c r="F999" t="inlineStr"/>
-      <c r="G999" t="n">
-        <v>0</v>
-      </c>
+      <c r="G999" t="inlineStr"/>
       <c r="H999" t="inlineStr"/>
-      <c r="I999" t="inlineStr"/>
+      <c r="I999" t="n">
+        <v>1</v>
+      </c>
       <c r="J999" t="inlineStr"/>
-      <c r="K999" t="inlineStr"/>
+      <c r="K999" t="n">
+        <v>1</v>
+      </c>
       <c r="L999" t="inlineStr"/>
       <c r="M999" t="inlineStr"/>
       <c r="N999" t="inlineStr"/>
@@ -32438,29 +32442,27 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>Chhetra BO</t>
+          <t>Ghillaur Kalan BO</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>L6253</t>
+          <t>H9418</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Mundlana SO</t>
+          <t>Sanghi SO</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr"/>
       <c r="E1000" t="inlineStr"/>
-      <c r="F1000" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1000" t="n">
-        <v>15</v>
-      </c>
+      <c r="F1000" t="inlineStr"/>
+      <c r="G1000" t="inlineStr"/>
       <c r="H1000" t="inlineStr"/>
-      <c r="I1000" t="inlineStr"/>
+      <c r="I1000" t="n">
+        <v>3</v>
+      </c>
       <c r="J1000" t="inlineStr"/>
       <c r="K1000" t="inlineStr"/>
       <c r="L1000" t="inlineStr"/>
@@ -32471,31 +32473,29 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>Dhurana BO</t>
+          <t>Girawar BO</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>L6255</t>
+          <t>H8969</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Mundlana SO</t>
+          <t>Madina SO</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr"/>
       <c r="E1001" t="inlineStr"/>
       <c r="F1001" t="inlineStr"/>
-      <c r="G1001" t="n">
-        <v>1</v>
-      </c>
+      <c r="G1001" t="inlineStr"/>
       <c r="H1001" t="inlineStr"/>
-      <c r="I1001" t="n">
-        <v>1</v>
-      </c>
+      <c r="I1001" t="inlineStr"/>
       <c r="J1001" t="inlineStr"/>
-      <c r="K1001" t="inlineStr"/>
+      <c r="K1001" t="n">
+        <v>52</v>
+      </c>
       <c r="L1001" t="inlineStr"/>
       <c r="M1001" t="inlineStr"/>
       <c r="N1001" t="inlineStr"/>
@@ -32504,25 +32504,25 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>Farmana SO</t>
+          <t>Janta Colony Rohtak SO</t>
         </is>
       </c>
       <c r="B1002" t="n">
-        <v>13140801</v>
+        <v>12400104</v>
       </c>
       <c r="C1002" t="inlineStr"/>
       <c r="D1002" t="inlineStr"/>
       <c r="E1002" t="inlineStr"/>
       <c r="F1002" t="inlineStr"/>
       <c r="G1002" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H1002" t="inlineStr"/>
-      <c r="I1002" t="n">
-        <v>1</v>
-      </c>
+      <c r="I1002" t="inlineStr"/>
       <c r="J1002" t="inlineStr"/>
-      <c r="K1002" t="inlineStr"/>
+      <c r="K1002" t="n">
+        <v>2</v>
+      </c>
       <c r="L1002" t="inlineStr"/>
       <c r="M1002" t="inlineStr"/>
       <c r="N1002" t="inlineStr"/>
@@ -32531,23 +32531,29 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>Gohana Mandi SO</t>
-        </is>
-      </c>
-      <c r="B1003" t="n">
-        <v>13130102</v>
-      </c>
-      <c r="C1003" t="inlineStr"/>
+          <t>Jassia BO</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>H9419</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Sanghi SO</t>
+        </is>
+      </c>
       <c r="D1003" t="inlineStr"/>
       <c r="E1003" t="inlineStr"/>
       <c r="F1003" t="inlineStr"/>
       <c r="G1003" t="inlineStr"/>
       <c r="H1003" t="inlineStr"/>
-      <c r="I1003" t="inlineStr"/>
+      <c r="I1003" t="n">
+        <v>3</v>
+      </c>
       <c r="J1003" t="inlineStr"/>
-      <c r="K1003" t="n">
-        <v>9</v>
-      </c>
+      <c r="K1003" t="inlineStr"/>
       <c r="L1003" t="inlineStr"/>
       <c r="M1003" t="inlineStr"/>
       <c r="N1003" t="inlineStr"/>
@@ -32556,26 +32562,30 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>Gohana SO</t>
-        </is>
-      </c>
-      <c r="B1004" t="n">
-        <v>13130103</v>
-      </c>
-      <c r="C1004" t="inlineStr"/>
+          <t>Jindran BO</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>H9420</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Sanghi SO</t>
+        </is>
+      </c>
       <c r="D1004" t="inlineStr"/>
       <c r="E1004" t="inlineStr"/>
       <c r="F1004" t="inlineStr"/>
-      <c r="G1004" t="n">
-        <v>1</v>
-      </c>
+      <c r="G1004" t="inlineStr"/>
       <c r="H1004" t="inlineStr"/>
       <c r="I1004" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1004" t="inlineStr"/>
       <c r="K1004" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L1004" t="inlineStr"/>
       <c r="M1004" t="inlineStr"/>
@@ -32585,29 +32595,25 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>Gopalpur BO</t>
-        </is>
-      </c>
-      <c r="B1005" t="inlineStr">
-        <is>
-          <t>J9554</t>
-        </is>
-      </c>
-      <c r="C1005" t="inlineStr">
-        <is>
-          <t>Kharkhauda SO</t>
-        </is>
-      </c>
+          <t>Kahnaur SO</t>
+        </is>
+      </c>
+      <c r="B1005" t="n">
+        <v>12441201</v>
+      </c>
+      <c r="C1005" t="inlineStr"/>
       <c r="D1005" t="inlineStr"/>
       <c r="E1005" t="inlineStr"/>
       <c r="F1005" t="inlineStr"/>
       <c r="G1005" t="inlineStr"/>
       <c r="H1005" t="inlineStr"/>
       <c r="I1005" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1005" t="inlineStr"/>
-      <c r="K1005" t="inlineStr"/>
+      <c r="K1005" t="n">
+        <v>3</v>
+      </c>
       <c r="L1005" t="inlineStr"/>
       <c r="M1005" t="inlineStr"/>
       <c r="N1005" t="inlineStr"/>
@@ -32616,29 +32622,29 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>Guhna BO</t>
+          <t>Kahri BO</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>M1774</t>
+          <t>B3545</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>Farmana SO</t>
+          <t>Machrauli SO</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr"/>
       <c r="E1006" t="inlineStr"/>
       <c r="F1006" t="inlineStr"/>
-      <c r="G1006" t="n">
-        <v>10</v>
-      </c>
+      <c r="G1006" t="inlineStr"/>
       <c r="H1006" t="inlineStr"/>
       <c r="I1006" t="inlineStr"/>
       <c r="J1006" t="inlineStr"/>
-      <c r="K1006" t="inlineStr"/>
+      <c r="K1006" t="n">
+        <v>1</v>
+      </c>
       <c r="L1006" t="inlineStr"/>
       <c r="M1006" t="inlineStr"/>
       <c r="N1006" t="inlineStr"/>
@@ -32647,31 +32653,25 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>Jagsi BO</t>
-        </is>
-      </c>
-      <c r="B1007" t="inlineStr">
-        <is>
-          <t>L4465</t>
-        </is>
-      </c>
-      <c r="C1007" t="inlineStr">
-        <is>
-          <t>Gohana SO</t>
-        </is>
-      </c>
+          <t>Kalanaur SO Rohtak</t>
+        </is>
+      </c>
+      <c r="B1007" t="n">
+        <v>12411301</v>
+      </c>
+      <c r="C1007" t="inlineStr"/>
       <c r="D1007" t="inlineStr"/>
       <c r="E1007" t="inlineStr"/>
       <c r="F1007" t="inlineStr"/>
-      <c r="G1007" t="inlineStr"/>
+      <c r="G1007" t="n">
+        <v>0</v>
+      </c>
       <c r="H1007" t="inlineStr"/>
       <c r="I1007" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J1007" t="inlineStr"/>
-      <c r="K1007" t="n">
-        <v>7</v>
-      </c>
+      <c r="K1007" t="inlineStr"/>
       <c r="L1007" t="inlineStr"/>
       <c r="M1007" t="inlineStr"/>
       <c r="N1007" t="inlineStr"/>
@@ -32680,31 +32680,27 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>Jawahra BO</t>
-        </is>
-      </c>
-      <c r="B1008" t="inlineStr">
-        <is>
-          <t>L6256</t>
-        </is>
-      </c>
-      <c r="C1008" t="inlineStr">
-        <is>
-          <t>Mundlana SO</t>
-        </is>
-      </c>
+          <t>Kansala SO</t>
+        </is>
+      </c>
+      <c r="B1008" t="n">
+        <v>12440601</v>
+      </c>
+      <c r="C1008" t="inlineStr"/>
       <c r="D1008" t="inlineStr"/>
       <c r="E1008" t="inlineStr"/>
       <c r="F1008" t="inlineStr"/>
       <c r="G1008" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H1008" t="inlineStr"/>
       <c r="I1008" t="n">
         <v>1</v>
       </c>
       <c r="J1008" t="inlineStr"/>
-      <c r="K1008" t="inlineStr"/>
+      <c r="K1008" t="n">
+        <v>1</v>
+      </c>
       <c r="L1008" t="inlineStr"/>
       <c r="M1008" t="inlineStr"/>
       <c r="N1008" t="inlineStr"/>
@@ -32713,27 +32709,29 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>Jhs Butana BO</t>
+          <t>Karontha BO</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>F7982</t>
+          <t>O0159</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Butana SO</t>
+          <t>Police Training Center Sunaria SO</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr"/>
       <c r="E1009" t="inlineStr"/>
-      <c r="F1009" t="inlineStr"/>
-      <c r="G1009" t="n">
-        <v>10</v>
-      </c>
+      <c r="F1009" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1009" t="inlineStr"/>
       <c r="H1009" t="inlineStr"/>
-      <c r="I1009" t="inlineStr"/>
+      <c r="I1009" t="n">
+        <v>1</v>
+      </c>
       <c r="J1009" t="inlineStr"/>
       <c r="K1009" t="inlineStr"/>
       <c r="L1009" t="inlineStr"/>
@@ -32744,21 +32742,27 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>Kanyagurukul Khanpur SO</t>
-        </is>
-      </c>
-      <c r="B1010" t="n">
-        <v>13130501</v>
-      </c>
-      <c r="C1010" t="inlineStr"/>
+          <t>Khairari BO</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>J2619</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Kalanaur SO Rohtak</t>
+        </is>
+      </c>
       <c r="D1010" t="inlineStr"/>
       <c r="E1010" t="inlineStr"/>
       <c r="F1010" t="inlineStr"/>
-      <c r="G1010" t="inlineStr"/>
+      <c r="G1010" t="n">
+        <v>1</v>
+      </c>
       <c r="H1010" t="inlineStr"/>
-      <c r="I1010" t="n">
-        <v>0</v>
-      </c>
+      <c r="I1010" t="inlineStr"/>
       <c r="J1010" t="inlineStr"/>
       <c r="K1010" t="inlineStr"/>
       <c r="L1010" t="inlineStr"/>
@@ -32769,17 +32773,17 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>Kasandi BO</t>
+          <t>Khidwali BO</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>E0707</t>
+          <t>H9422</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Kanyagurukul Khanpur SO</t>
+          <t>Sanghi SO</t>
         </is>
       </c>
       <c r="D1011" t="inlineStr"/>
@@ -32787,11 +32791,11 @@
       <c r="F1011" t="inlineStr"/>
       <c r="G1011" t="inlineStr"/>
       <c r="H1011" t="inlineStr"/>
-      <c r="I1011" t="n">
-        <v>2</v>
-      </c>
+      <c r="I1011" t="inlineStr"/>
       <c r="J1011" t="inlineStr"/>
-      <c r="K1011" t="inlineStr"/>
+      <c r="K1011" t="n">
+        <v>1</v>
+      </c>
       <c r="L1011" t="inlineStr"/>
       <c r="M1011" t="inlineStr"/>
       <c r="N1011" t="inlineStr"/>
@@ -32800,28 +32804,26 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>Kathura BO</t>
-        </is>
-      </c>
-      <c r="B1012" t="inlineStr">
-        <is>
-          <t>L4468</t>
-        </is>
-      </c>
-      <c r="C1012" t="inlineStr">
-        <is>
-          <t>Gohana SO</t>
-        </is>
-      </c>
+          <t>Lakhan Majra SO</t>
+        </is>
+      </c>
+      <c r="B1012" t="n">
+        <v>12451401</v>
+      </c>
+      <c r="C1012" t="inlineStr"/>
       <c r="D1012" t="inlineStr"/>
       <c r="E1012" t="inlineStr"/>
       <c r="F1012" t="inlineStr"/>
-      <c r="G1012" t="inlineStr"/>
+      <c r="G1012" t="n">
+        <v>0</v>
+      </c>
       <c r="H1012" t="inlineStr"/>
-      <c r="I1012" t="inlineStr"/>
+      <c r="I1012" t="n">
+        <v>1</v>
+      </c>
       <c r="J1012" t="inlineStr"/>
       <c r="K1012" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L1012" t="inlineStr"/>
       <c r="M1012" t="inlineStr"/>
@@ -32831,26 +32833,24 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>Kharkhauda SO</t>
+          <t>Madina SO</t>
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>13140201</v>
+        <v>12411101</v>
       </c>
       <c r="C1013" t="inlineStr"/>
       <c r="D1013" t="inlineStr"/>
       <c r="E1013" t="inlineStr"/>
       <c r="F1013" t="inlineStr"/>
       <c r="G1013" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H1013" t="inlineStr"/>
-      <c r="I1013" t="n">
-        <v>1</v>
-      </c>
+      <c r="I1013" t="inlineStr"/>
       <c r="J1013" t="inlineStr"/>
       <c r="K1013" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1013" t="inlineStr"/>
       <c r="M1013" t="inlineStr"/>
@@ -32860,58 +32860,50 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>Kheri Damkan BO</t>
-        </is>
-      </c>
-      <c r="B1014" t="inlineStr">
-        <is>
-          <t>L4470</t>
-        </is>
-      </c>
-      <c r="C1014" t="inlineStr">
-        <is>
-          <t>Gohana SO</t>
-        </is>
-      </c>
+          <t>Model Town SO Rohtak</t>
+        </is>
+      </c>
+      <c r="B1014" t="n">
+        <v>12400107</v>
+      </c>
+      <c r="C1014" t="inlineStr"/>
       <c r="D1014" t="inlineStr"/>
       <c r="E1014" t="inlineStr"/>
       <c r="F1014" t="inlineStr"/>
-      <c r="G1014" t="inlineStr"/>
+      <c r="G1014" t="n">
+        <v>2</v>
+      </c>
       <c r="H1014" t="inlineStr"/>
-      <c r="I1014" t="n">
+      <c r="I1014" t="inlineStr"/>
+      <c r="J1014" t="inlineStr"/>
+      <c r="K1014" t="n">
         <v>3</v>
       </c>
-      <c r="J1014" t="inlineStr"/>
-      <c r="K1014" t="inlineStr"/>
       <c r="L1014" t="inlineStr"/>
       <c r="M1014" t="inlineStr"/>
-      <c r="N1014" t="inlineStr"/>
+      <c r="N1014" t="n">
+        <v>3</v>
+      </c>
       <c r="O1014" t="inlineStr"/>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>Madina BO</t>
-        </is>
-      </c>
-      <c r="B1015" t="inlineStr">
-        <is>
-          <t>L4472</t>
-        </is>
-      </c>
-      <c r="C1015" t="inlineStr">
-        <is>
-          <t>Gohana SO</t>
-        </is>
-      </c>
+          <t>Mokhra SO</t>
+        </is>
+      </c>
+      <c r="B1015" t="n">
+        <v>12402201</v>
+      </c>
+      <c r="C1015" t="inlineStr"/>
       <c r="D1015" t="inlineStr"/>
       <c r="E1015" t="inlineStr"/>
       <c r="F1015" t="inlineStr"/>
-      <c r="G1015" t="inlineStr"/>
+      <c r="G1015" t="n">
+        <v>1</v>
+      </c>
       <c r="H1015" t="inlineStr"/>
-      <c r="I1015" t="n">
-        <v>1</v>
-      </c>
+      <c r="I1015" t="inlineStr"/>
       <c r="J1015" t="inlineStr"/>
       <c r="K1015" t="inlineStr"/>
       <c r="L1015" t="inlineStr"/>
@@ -32922,29 +32914,25 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>MahraI BO</t>
-        </is>
-      </c>
-      <c r="B1016" t="inlineStr">
-        <is>
-          <t>L4473</t>
-        </is>
-      </c>
-      <c r="C1016" t="inlineStr">
-        <is>
-          <t>Gohana SO</t>
-        </is>
-      </c>
+          <t>Nindana SO</t>
+        </is>
+      </c>
+      <c r="B1016" t="n">
+        <v>12451301</v>
+      </c>
+      <c r="C1016" t="inlineStr"/>
       <c r="D1016" t="inlineStr"/>
       <c r="E1016" t="inlineStr"/>
       <c r="F1016" t="inlineStr"/>
       <c r="G1016" t="inlineStr"/>
       <c r="H1016" t="inlineStr"/>
       <c r="I1016" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J1016" t="inlineStr"/>
-      <c r="K1016" t="inlineStr"/>
+      <c r="K1016" t="n">
+        <v>0</v>
+      </c>
       <c r="L1016" t="inlineStr"/>
       <c r="M1016" t="inlineStr"/>
       <c r="N1016" t="inlineStr"/>
@@ -32953,11 +32941,11 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>Mundlana SO</t>
+          <t>Police Training Center Sunaria SO</t>
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>13130601</v>
+        <v>12401001</v>
       </c>
       <c r="C1017" t="inlineStr"/>
       <c r="D1017" t="inlineStr"/>
@@ -32965,15 +32953,15 @@
       <c r="F1017" t="n">
         <v>0</v>
       </c>
-      <c r="G1017" t="n">
-        <v>0</v>
-      </c>
+      <c r="G1017" t="inlineStr"/>
       <c r="H1017" t="inlineStr"/>
       <c r="I1017" t="n">
         <v>0</v>
       </c>
       <c r="J1017" t="inlineStr"/>
-      <c r="K1017" t="inlineStr"/>
+      <c r="K1017" t="n">
+        <v>0</v>
+      </c>
       <c r="L1017" t="inlineStr"/>
       <c r="M1017" t="inlineStr"/>
       <c r="N1017" t="inlineStr"/>
@@ -32982,29 +32970,31 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>Nuran Khera BO</t>
-        </is>
-      </c>
-      <c r="B1018" t="inlineStr">
-        <is>
-          <t>F7984</t>
-        </is>
-      </c>
-      <c r="C1018" t="inlineStr">
-        <is>
-          <t>Butana SO</t>
-        </is>
-      </c>
+          <t>Rohtak HO</t>
+        </is>
+      </c>
+      <c r="B1018" t="n">
+        <v>12400100</v>
+      </c>
+      <c r="C1018" t="inlineStr"/>
       <c r="D1018" t="inlineStr"/>
       <c r="E1018" t="inlineStr"/>
-      <c r="F1018" t="inlineStr"/>
+      <c r="F1018" t="n">
+        <v>2</v>
+      </c>
       <c r="G1018" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1018" t="inlineStr"/>
-      <c r="I1018" t="inlineStr"/>
-      <c r="J1018" t="inlineStr"/>
-      <c r="K1018" t="inlineStr"/>
+      <c r="I1018" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1018" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1018" t="n">
+        <v>11</v>
+      </c>
       <c r="L1018" t="inlineStr"/>
       <c r="M1018" t="inlineStr"/>
       <c r="N1018" t="inlineStr"/>
@@ -33013,27 +33003,29 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>Pipli BO</t>
+          <t>Sampel BO</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>J9558</t>
+          <t>J2621</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Kharkhauda SO</t>
+          <t>Kalanaur SO Rohtak</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr"/>
       <c r="E1019" t="inlineStr"/>
       <c r="F1019" t="inlineStr"/>
       <c r="G1019" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1019" t="inlineStr"/>
-      <c r="I1019" t="inlineStr"/>
+      <c r="I1019" t="n">
+        <v>1</v>
+      </c>
       <c r="J1019" t="inlineStr"/>
       <c r="K1019" t="inlineStr"/>
       <c r="L1019" t="inlineStr"/>
@@ -33044,29 +33036,27 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>Saragthal BO</t>
-        </is>
-      </c>
-      <c r="B1020" t="inlineStr">
-        <is>
-          <t>A7184</t>
-        </is>
-      </c>
-      <c r="C1020" t="inlineStr">
-        <is>
-          <t>Kanyagurukul Khanpur SO</t>
-        </is>
-      </c>
+          <t>Sanghi SO</t>
+        </is>
+      </c>
+      <c r="B1020" t="n">
+        <v>12430301</v>
+      </c>
+      <c r="C1020" t="inlineStr"/>
       <c r="D1020" t="inlineStr"/>
-      <c r="E1020" t="inlineStr"/>
+      <c r="E1020" t="n">
+        <v>1</v>
+      </c>
       <c r="F1020" t="inlineStr"/>
       <c r="G1020" t="inlineStr"/>
       <c r="H1020" t="inlineStr"/>
       <c r="I1020" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1020" t="inlineStr"/>
-      <c r="K1020" t="inlineStr"/>
+      <c r="K1020" t="n">
+        <v>0</v>
+      </c>
       <c r="L1020" t="inlineStr"/>
       <c r="M1020" t="inlineStr"/>
       <c r="N1020" t="inlineStr"/>
@@ -33075,95 +33065,81 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>Sonipat HO</t>
-        </is>
-      </c>
-      <c r="B1021" t="n">
-        <v>13100100</v>
-      </c>
-      <c r="C1021" t="inlineStr"/>
-      <c r="D1021" t="n">
-        <v>2</v>
-      </c>
+          <t>Singhpura Kalan BO</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>C8462</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Lakhan Majra SO</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr"/>
       <c r="E1021" t="inlineStr"/>
-      <c r="F1021" t="n">
-        <v>1</v>
-      </c>
+      <c r="F1021" t="inlineStr"/>
       <c r="G1021" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H1021" t="inlineStr"/>
-      <c r="I1021" t="n">
-        <v>11</v>
-      </c>
-      <c r="J1021" t="n">
-        <v>2</v>
-      </c>
-      <c r="K1021" t="n">
-        <v>8</v>
-      </c>
+      <c r="I1021" t="inlineStr"/>
+      <c r="J1021" t="inlineStr"/>
+      <c r="K1021" t="inlineStr"/>
       <c r="L1021" t="inlineStr"/>
       <c r="M1021" t="inlineStr"/>
-      <c r="N1021" t="n">
-        <v>4</v>
-      </c>
+      <c r="N1021" t="inlineStr"/>
       <c r="O1021" t="inlineStr"/>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>Total:</t>
-        </is>
-      </c>
-      <c r="B1022" t="inlineStr"/>
-      <c r="C1022" t="inlineStr"/>
-      <c r="D1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="F1022" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1022" t="n">
-        <v>63</v>
-      </c>
-      <c r="H1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1022" t="n">
-        <v>22</v>
-      </c>
-      <c r="J1022" t="n">
-        <v>0</v>
-      </c>
+          <t>Sisarkhas BO</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>J9571</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Mehem SO</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr"/>
+      <c r="E1022" t="inlineStr"/>
+      <c r="F1022" t="inlineStr"/>
+      <c r="G1022" t="inlineStr"/>
+      <c r="H1022" t="inlineStr"/>
+      <c r="I1022" t="inlineStr"/>
+      <c r="J1022" t="inlineStr"/>
       <c r="K1022" t="n">
-        <v>48</v>
-      </c>
-      <c r="L1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="N1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="O1022" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L1022" t="inlineStr"/>
+      <c r="M1022" t="inlineStr"/>
+      <c r="N1022" t="inlineStr"/>
+      <c r="O1022" t="inlineStr"/>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Product Wise A/C Report
-</t>
-        </is>
-      </c>
-      <c r="B1023" t="inlineStr"/>
-      <c r="C1023" t="inlineStr"/>
+          <t>Sundana BO</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>J8919</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Kahnaur SO</t>
+        </is>
+      </c>
       <c r="D1023" t="inlineStr"/>
       <c r="E1023" t="inlineStr"/>
       <c r="F1023" t="inlineStr"/>
@@ -33171,7 +33147,9 @@
       <c r="H1023" t="inlineStr"/>
       <c r="I1023" t="inlineStr"/>
       <c r="J1023" t="inlineStr"/>
-      <c r="K1023" t="inlineStr"/>
+      <c r="K1023" t="n">
+        <v>2</v>
+      </c>
       <c r="L1023" t="inlineStr"/>
       <c r="M1023" t="inlineStr"/>
       <c r="N1023" t="inlineStr"/>
@@ -33180,110 +33158,66 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1024" t="inlineStr">
-        <is>
-          <t>SOL ID / BOCODE</t>
-        </is>
-      </c>
-      <c r="C1024" t="inlineStr">
-        <is>
-          <t>SO Name</t>
-        </is>
-      </c>
-      <c r="D1024" t="inlineStr">
-        <is>
-          <t>MIS</t>
-        </is>
-      </c>
-      <c r="E1024" t="inlineStr">
-        <is>
-          <t>PPFGP</t>
-        </is>
-      </c>
-      <c r="F1024" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="G1024" t="inlineStr">
-        <is>
-          <t>RD</t>
-        </is>
-      </c>
-      <c r="H1024" t="inlineStr">
-        <is>
-          <t>SBBAS</t>
-        </is>
-      </c>
-      <c r="I1024" t="inlineStr">
-        <is>
-          <t>SBSGP</t>
-        </is>
-      </c>
-      <c r="J1024" t="inlineStr">
-        <is>
-          <t>SCSS</t>
-        </is>
-      </c>
-      <c r="K1024" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="L1024" t="inlineStr">
-        <is>
-          <t>PRFTS</t>
-        </is>
-      </c>
-      <c r="M1024" t="inlineStr">
-        <is>
-          <t>KVN</t>
-        </is>
-      </c>
-      <c r="N1024" t="inlineStr">
-        <is>
-          <t>NSC8</t>
-        </is>
-      </c>
-      <c r="O1024" t="inlineStr">
-        <is>
-          <t>MSSC</t>
-        </is>
+          <t>Total:</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr"/>
+      <c r="C1024" t="inlineStr"/>
+      <c r="D1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>16</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1024" t="n">
+        <v>19</v>
+      </c>
+      <c r="J1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1024" t="n">
+        <v>76</v>
+      </c>
+      <c r="L1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1024" t="n">
+        <v>3</v>
+      </c>
+      <c r="O1024" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>AhulanaGannur BO</t>
-        </is>
-      </c>
-      <c r="B1025" t="inlineStr">
-        <is>
-          <t>A8170</t>
-        </is>
-      </c>
-      <c r="C1025" t="inlineStr">
-        <is>
-          <t>Ganaur SO</t>
-        </is>
-      </c>
+          <t xml:space="preserve">
+Product Wise A/C Report
+</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr"/>
+      <c r="C1025" t="inlineStr"/>
       <c r="D1025" t="inlineStr"/>
       <c r="E1025" t="inlineStr"/>
       <c r="F1025" t="inlineStr"/>
-      <c r="G1025" t="n">
-        <v>1</v>
-      </c>
+      <c r="G1025" t="inlineStr"/>
       <c r="H1025" t="inlineStr"/>
-      <c r="I1025" t="n">
-        <v>1</v>
-      </c>
+      <c r="I1025" t="inlineStr"/>
       <c r="J1025" t="inlineStr"/>
-      <c r="K1025" t="n">
-        <v>1</v>
-      </c>
+      <c r="K1025" t="inlineStr"/>
       <c r="L1025" t="inlineStr"/>
       <c r="M1025" t="inlineStr"/>
       <c r="N1025" t="inlineStr"/>
@@ -33292,51 +33226,103 @@
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>Atlas Cycle SO</t>
-        </is>
-      </c>
-      <c r="B1026" t="n">
-        <v>13100101</v>
-      </c>
-      <c r="C1026" t="inlineStr"/>
-      <c r="D1026" t="inlineStr"/>
-      <c r="E1026" t="inlineStr"/>
-      <c r="F1026" t="inlineStr"/>
-      <c r="G1026" t="n">
-        <v>1</v>
-      </c>
-      <c r="H1026" t="inlineStr"/>
-      <c r="I1026" t="n">
-        <v>2</v>
-      </c>
-      <c r="J1026" t="inlineStr"/>
-      <c r="K1026" t="inlineStr"/>
-      <c r="L1026" t="inlineStr"/>
-      <c r="M1026" t="inlineStr"/>
-      <c r="N1026" t="n">
-        <v>1</v>
-      </c>
-      <c r="O1026" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>SOL ID / BOCODE</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>SO Name</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>MIS</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>PPFGP</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>SBBAS</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>SBSGP</t>
+        </is>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>SCSS</t>
+        </is>
+      </c>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="L1026" t="inlineStr">
+        <is>
+          <t>PRFTS</t>
+        </is>
+      </c>
+      <c r="M1026" t="inlineStr">
+        <is>
+          <t>KVN</t>
+        </is>
+      </c>
+      <c r="N1026" t="inlineStr">
+        <is>
+          <t>NSC8</t>
+        </is>
+      </c>
+      <c r="O1026" t="inlineStr">
+        <is>
+          <t>MSSC</t>
+        </is>
+      </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>Bahalgarh SO</t>
-        </is>
-      </c>
-      <c r="B1027" t="n">
-        <v>13102101</v>
-      </c>
-      <c r="C1027" t="inlineStr"/>
+          <t>AhulanaGohana BO</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>L4458</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Gohana SO</t>
+        </is>
+      </c>
       <c r="D1027" t="inlineStr"/>
       <c r="E1027" t="inlineStr"/>
       <c r="F1027" t="inlineStr"/>
-      <c r="G1027" t="n">
-        <v>0</v>
-      </c>
+      <c r="G1027" t="inlineStr"/>
       <c r="H1027" t="inlineStr"/>
       <c r="I1027" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J1027" t="inlineStr"/>
       <c r="K1027" t="inlineStr"/>
@@ -33348,17 +33334,17 @@
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>Bayanpur BO</t>
+          <t>Barona BO</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
         <is>
-          <t>B7816</t>
+          <t>J9551</t>
         </is>
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Sonipat HO</t>
+          <t>Kharkhauda SO</t>
         </is>
       </c>
       <c r="D1028" t="inlineStr"/>
@@ -33369,7 +33355,7 @@
       <c r="I1028" t="inlineStr"/>
       <c r="J1028" t="inlineStr"/>
       <c r="K1028" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="L1028" t="inlineStr"/>
       <c r="M1028" t="inlineStr"/>
@@ -33379,27 +33365,29 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>Bhatgaon SO Sonipat</t>
-        </is>
-      </c>
-      <c r="B1029" t="n">
-        <v>13102201</v>
-      </c>
-      <c r="C1029" t="inlineStr"/>
+          <t>Busana BO</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>L6252</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Mundlana SO</t>
+        </is>
+      </c>
       <c r="D1029" t="inlineStr"/>
       <c r="E1029" t="inlineStr"/>
       <c r="F1029" t="inlineStr"/>
       <c r="G1029" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H1029" t="inlineStr"/>
-      <c r="I1029" t="n">
-        <v>2</v>
-      </c>
+      <c r="I1029" t="inlineStr"/>
       <c r="J1029" t="inlineStr"/>
-      <c r="K1029" t="n">
-        <v>2</v>
-      </c>
+      <c r="K1029" t="inlineStr"/>
       <c r="L1029" t="inlineStr"/>
       <c r="M1029" t="inlineStr"/>
       <c r="N1029" t="inlineStr"/>
@@ -33408,27 +33396,21 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>Bindroli BO</t>
-        </is>
-      </c>
-      <c r="B1030" t="inlineStr">
-        <is>
-          <t>M0952</t>
-        </is>
-      </c>
-      <c r="C1030" t="inlineStr">
-        <is>
-          <t>Rohat SO Sonipat</t>
-        </is>
-      </c>
+          <t>Butana SO</t>
+        </is>
+      </c>
+      <c r="B1030" t="n">
+        <v>13130201</v>
+      </c>
+      <c r="C1030" t="inlineStr"/>
       <c r="D1030" t="inlineStr"/>
       <c r="E1030" t="inlineStr"/>
       <c r="F1030" t="inlineStr"/>
-      <c r="G1030" t="inlineStr"/>
+      <c r="G1030" t="n">
+        <v>0</v>
+      </c>
       <c r="H1030" t="inlineStr"/>
-      <c r="I1030" t="n">
-        <v>1</v>
-      </c>
+      <c r="I1030" t="inlineStr"/>
       <c r="J1030" t="inlineStr"/>
       <c r="K1030" t="inlineStr"/>
       <c r="L1030" t="inlineStr"/>
@@ -33439,25 +33421,27 @@
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>Bohla BO</t>
+          <t>Chhetra BO</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>L8602</t>
+          <t>L6253</t>
         </is>
       </c>
       <c r="C1031" t="inlineStr">
         <is>
-          <t>Juan SO</t>
+          <t>Mundlana SO</t>
         </is>
       </c>
       <c r="D1031" t="inlineStr"/>
       <c r="E1031" t="inlineStr"/>
       <c r="F1031" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1031" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>15</v>
+      </c>
       <c r="H1031" t="inlineStr"/>
       <c r="I1031" t="inlineStr"/>
       <c r="J1031" t="inlineStr"/>
@@ -33470,17 +33454,17 @@
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>Datauli BO</t>
+          <t>Dhurana BO</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>D3377</t>
+          <t>L6255</t>
         </is>
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Ganaur SO</t>
+          <t>Mundlana SO</t>
         </is>
       </c>
       <c r="D1032" t="inlineStr"/>
@@ -33490,7 +33474,9 @@
         <v>1</v>
       </c>
       <c r="H1032" t="inlineStr"/>
-      <c r="I1032" t="inlineStr"/>
+      <c r="I1032" t="n">
+        <v>1</v>
+      </c>
       <c r="J1032" t="inlineStr"/>
       <c r="K1032" t="inlineStr"/>
       <c r="L1032" t="inlineStr"/>
@@ -33501,27 +33487,25 @@
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>Ganaur City SO</t>
+          <t>Farmana SO</t>
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>13110101</v>
+        <v>13140801</v>
       </c>
       <c r="C1033" t="inlineStr"/>
       <c r="D1033" t="inlineStr"/>
       <c r="E1033" t="inlineStr"/>
       <c r="F1033" t="inlineStr"/>
       <c r="G1033" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H1033" t="inlineStr"/>
       <c r="I1033" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1033" t="inlineStr"/>
-      <c r="K1033" t="n">
-        <v>4</v>
-      </c>
+      <c r="K1033" t="inlineStr"/>
       <c r="L1033" t="inlineStr"/>
       <c r="M1033" t="inlineStr"/>
       <c r="N1033" t="inlineStr"/>
@@ -33530,26 +33514,22 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>Ganaur SO</t>
+          <t>Gohana Mandi SO</t>
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>13110102</v>
+        <v>13130102</v>
       </c>
       <c r="C1034" t="inlineStr"/>
       <c r="D1034" t="inlineStr"/>
       <c r="E1034" t="inlineStr"/>
       <c r="F1034" t="inlineStr"/>
-      <c r="G1034" t="n">
-        <v>0</v>
-      </c>
+      <c r="G1034" t="inlineStr"/>
       <c r="H1034" t="inlineStr"/>
-      <c r="I1034" t="n">
-        <v>1</v>
-      </c>
+      <c r="I1034" t="inlineStr"/>
       <c r="J1034" t="inlineStr"/>
       <c r="K1034" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L1034" t="inlineStr"/>
       <c r="M1034" t="inlineStr"/>
@@ -33559,19 +33539,23 @@
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>Gohana Road SO Sonipat</t>
+          <t>Gohana SO</t>
         </is>
       </c>
       <c r="B1035" t="n">
-        <v>13100104</v>
+        <v>13130103</v>
       </c>
       <c r="C1035" t="inlineStr"/>
       <c r="D1035" t="inlineStr"/>
       <c r="E1035" t="inlineStr"/>
       <c r="F1035" t="inlineStr"/>
-      <c r="G1035" t="inlineStr"/>
+      <c r="G1035" t="n">
+        <v>1</v>
+      </c>
       <c r="H1035" t="inlineStr"/>
-      <c r="I1035" t="inlineStr"/>
+      <c r="I1035" t="n">
+        <v>1</v>
+      </c>
       <c r="J1035" t="inlineStr"/>
       <c r="K1035" t="n">
         <v>5</v>
@@ -33584,33 +33568,29 @@
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>Harsana Kalan BO</t>
+          <t>Gopalpur BO</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>A0936</t>
+          <t>J9554</t>
         </is>
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Sonipat HO</t>
+          <t>Kharkhauda SO</t>
         </is>
       </c>
       <c r="D1036" t="inlineStr"/>
       <c r="E1036" t="inlineStr"/>
-      <c r="F1036" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1036" t="n">
-        <v>1</v>
-      </c>
+      <c r="F1036" t="inlineStr"/>
+      <c r="G1036" t="inlineStr"/>
       <c r="H1036" t="inlineStr"/>
-      <c r="I1036" t="inlineStr"/>
+      <c r="I1036" t="n">
+        <v>1</v>
+      </c>
       <c r="J1036" t="inlineStr"/>
-      <c r="K1036" t="n">
-        <v>2</v>
-      </c>
+      <c r="K1036" t="inlineStr"/>
       <c r="L1036" t="inlineStr"/>
       <c r="M1036" t="inlineStr"/>
       <c r="N1036" t="inlineStr"/>
@@ -33619,29 +33599,29 @@
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>Industrial Estate Kundli SO</t>
-        </is>
-      </c>
-      <c r="B1037" t="n">
-        <v>13102801</v>
-      </c>
-      <c r="C1037" t="inlineStr"/>
+          <t>Guhna BO</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>M1774</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Farmana SO</t>
+        </is>
+      </c>
       <c r="D1037" t="inlineStr"/>
       <c r="E1037" t="inlineStr"/>
-      <c r="F1037" t="n">
-        <v>1</v>
-      </c>
+      <c r="F1037" t="inlineStr"/>
       <c r="G1037" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H1037" t="inlineStr"/>
-      <c r="I1037" t="n">
-        <v>0</v>
-      </c>
+      <c r="I1037" t="inlineStr"/>
       <c r="J1037" t="inlineStr"/>
-      <c r="K1037" t="n">
-        <v>0</v>
-      </c>
+      <c r="K1037" t="inlineStr"/>
       <c r="L1037" t="inlineStr"/>
       <c r="M1037" t="inlineStr"/>
       <c r="N1037" t="inlineStr"/>
@@ -33650,23 +33630,31 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>Jakhauli SO</t>
-        </is>
-      </c>
-      <c r="B1038" t="n">
-        <v>13102301</v>
-      </c>
-      <c r="C1038" t="inlineStr"/>
+          <t>Jagsi BO</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>L4465</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Gohana SO</t>
+        </is>
+      </c>
       <c r="D1038" t="inlineStr"/>
       <c r="E1038" t="inlineStr"/>
       <c r="F1038" t="inlineStr"/>
       <c r="G1038" t="inlineStr"/>
       <c r="H1038" t="inlineStr"/>
-      <c r="I1038" t="inlineStr"/>
-      <c r="J1038" t="n">
-        <v>1</v>
-      </c>
-      <c r="K1038" t="inlineStr"/>
+      <c r="I1038" t="n">
+        <v>6</v>
+      </c>
+      <c r="J1038" t="inlineStr"/>
+      <c r="K1038" t="n">
+        <v>7</v>
+      </c>
       <c r="L1038" t="inlineStr"/>
       <c r="M1038" t="inlineStr"/>
       <c r="N1038" t="inlineStr"/>
@@ -33675,33 +33663,31 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>Janti Kalan BO</t>
+          <t>Jawahra BO</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>F7688</t>
+          <t>L6256</t>
         </is>
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Industrial Estate Kundli SO</t>
+          <t>Mundlana SO</t>
         </is>
       </c>
       <c r="D1039" t="inlineStr"/>
       <c r="E1039" t="inlineStr"/>
       <c r="F1039" t="inlineStr"/>
       <c r="G1039" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H1039" t="inlineStr"/>
       <c r="I1039" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1039" t="inlineStr"/>
-      <c r="K1039" t="n">
-        <v>9</v>
-      </c>
+      <c r="K1039" t="inlineStr"/>
       <c r="L1039" t="inlineStr"/>
       <c r="M1039" t="inlineStr"/>
       <c r="N1039" t="inlineStr"/>
@@ -33710,27 +33696,29 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>Juan SO</t>
-        </is>
-      </c>
-      <c r="B1040" t="n">
-        <v>13102401</v>
-      </c>
-      <c r="C1040" t="inlineStr"/>
+          <t>Jhs Butana BO</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>F7982</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Butana SO</t>
+        </is>
+      </c>
       <c r="D1040" t="inlineStr"/>
       <c r="E1040" t="inlineStr"/>
-      <c r="F1040" t="n">
-        <v>0</v>
-      </c>
+      <c r="F1040" t="inlineStr"/>
       <c r="G1040" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H1040" t="inlineStr"/>
       <c r="I1040" t="inlineStr"/>
       <c r="J1040" t="inlineStr"/>
-      <c r="K1040" t="n">
-        <v>1</v>
-      </c>
+      <c r="K1040" t="inlineStr"/>
       <c r="L1040" t="inlineStr"/>
       <c r="M1040" t="inlineStr"/>
       <c r="N1040" t="inlineStr"/>
@@ -33739,27 +33727,21 @@
     <row r="1041">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>Karewari BO</t>
-        </is>
-      </c>
-      <c r="B1041" t="inlineStr">
-        <is>
-          <t>L8603</t>
-        </is>
-      </c>
-      <c r="C1041" t="inlineStr">
-        <is>
-          <t>Juan SO</t>
-        </is>
-      </c>
+          <t>Kanyagurukul Khanpur SO</t>
+        </is>
+      </c>
+      <c r="B1041" t="n">
+        <v>13130501</v>
+      </c>
+      <c r="C1041" t="inlineStr"/>
       <c r="D1041" t="inlineStr"/>
       <c r="E1041" t="inlineStr"/>
-      <c r="F1041" t="n">
-        <v>1</v>
-      </c>
+      <c r="F1041" t="inlineStr"/>
       <c r="G1041" t="inlineStr"/>
       <c r="H1041" t="inlineStr"/>
-      <c r="I1041" t="inlineStr"/>
+      <c r="I1041" t="n">
+        <v>0</v>
+      </c>
       <c r="J1041" t="inlineStr"/>
       <c r="K1041" t="inlineStr"/>
       <c r="L1041" t="inlineStr"/>
@@ -33770,17 +33752,17 @@
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>Kheri Manajat BO</t>
+          <t>Kasandi BO</t>
         </is>
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>M1780</t>
+          <t>E0707</t>
         </is>
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Nahri SO</t>
+          <t>Kanyagurukul Khanpur SO</t>
         </is>
       </c>
       <c r="D1042" t="inlineStr"/>
@@ -33788,11 +33770,11 @@
       <c r="F1042" t="inlineStr"/>
       <c r="G1042" t="inlineStr"/>
       <c r="H1042" t="inlineStr"/>
-      <c r="I1042" t="inlineStr"/>
+      <c r="I1042" t="n">
+        <v>2</v>
+      </c>
       <c r="J1042" t="inlineStr"/>
-      <c r="K1042" t="n">
-        <v>1</v>
-      </c>
+      <c r="K1042" t="inlineStr"/>
       <c r="L1042" t="inlineStr"/>
       <c r="M1042" t="inlineStr"/>
       <c r="N1042" t="inlineStr"/>
@@ -33801,31 +33783,29 @@
     <row r="1043">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>Khewra BO</t>
+          <t>Kathura BO</t>
         </is>
       </c>
       <c r="B1043" t="inlineStr">
         <is>
-          <t>O0186</t>
+          <t>L4468</t>
         </is>
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Bahalgarh SO</t>
+          <t>Gohana SO</t>
         </is>
       </c>
       <c r="D1043" t="inlineStr"/>
       <c r="E1043" t="inlineStr"/>
       <c r="F1043" t="inlineStr"/>
-      <c r="G1043" t="n">
-        <v>1</v>
-      </c>
+      <c r="G1043" t="inlineStr"/>
       <c r="H1043" t="inlineStr"/>
-      <c r="I1043" t="n">
-        <v>2</v>
-      </c>
+      <c r="I1043" t="inlineStr"/>
       <c r="J1043" t="inlineStr"/>
-      <c r="K1043" t="inlineStr"/>
+      <c r="K1043" t="n">
+        <v>4</v>
+      </c>
       <c r="L1043" t="inlineStr"/>
       <c r="M1043" t="inlineStr"/>
       <c r="N1043" t="inlineStr"/>
@@ -33834,28 +33814,26 @@
     <row r="1044">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>Khubru BO</t>
-        </is>
-      </c>
-      <c r="B1044" t="inlineStr">
-        <is>
-          <t>E1660</t>
-        </is>
-      </c>
-      <c r="C1044" t="inlineStr">
-        <is>
-          <t>Ganaur SO</t>
-        </is>
-      </c>
+          <t>Kharkhauda SO</t>
+        </is>
+      </c>
+      <c r="B1044" t="n">
+        <v>13140201</v>
+      </c>
+      <c r="C1044" t="inlineStr"/>
       <c r="D1044" t="inlineStr"/>
       <c r="E1044" t="inlineStr"/>
       <c r="F1044" t="inlineStr"/>
-      <c r="G1044" t="inlineStr"/>
+      <c r="G1044" t="n">
+        <v>0</v>
+      </c>
       <c r="H1044" t="inlineStr"/>
-      <c r="I1044" t="inlineStr"/>
+      <c r="I1044" t="n">
+        <v>1</v>
+      </c>
       <c r="J1044" t="inlineStr"/>
       <c r="K1044" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L1044" t="inlineStr"/>
       <c r="M1044" t="inlineStr"/>
@@ -33865,17 +33843,17 @@
     <row r="1045">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>Lehrara BO</t>
+          <t>Kheri Damkan BO</t>
         </is>
       </c>
       <c r="B1045" t="inlineStr">
         <is>
-          <t>C6243</t>
+          <t>L4470</t>
         </is>
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Sonipat HO</t>
+          <t>Gohana SO</t>
         </is>
       </c>
       <c r="D1045" t="inlineStr"/>
@@ -33884,12 +33862,10 @@
       <c r="G1045" t="inlineStr"/>
       <c r="H1045" t="inlineStr"/>
       <c r="I1045" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J1045" t="inlineStr"/>
-      <c r="K1045" t="n">
-        <v>1</v>
-      </c>
+      <c r="K1045" t="inlineStr"/>
       <c r="L1045" t="inlineStr"/>
       <c r="M1045" t="inlineStr"/>
       <c r="N1045" t="inlineStr"/>
@@ -33898,27 +33874,27 @@
     <row r="1046">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>Mandaura BO</t>
+          <t>Madina BO</t>
         </is>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>M1781</t>
+          <t>L4472</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Nahri SO</t>
+          <t>Gohana SO</t>
         </is>
       </c>
       <c r="D1046" t="inlineStr"/>
       <c r="E1046" t="inlineStr"/>
-      <c r="F1046" t="n">
-        <v>1</v>
-      </c>
+      <c r="F1046" t="inlineStr"/>
       <c r="G1046" t="inlineStr"/>
       <c r="H1046" t="inlineStr"/>
-      <c r="I1046" t="inlineStr"/>
+      <c r="I1046" t="n">
+        <v>1</v>
+      </c>
       <c r="J1046" t="inlineStr"/>
       <c r="K1046" t="inlineStr"/>
       <c r="L1046" t="inlineStr"/>
@@ -33929,17 +33905,17 @@
     <row r="1047">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>Mehlana BO</t>
+          <t>MahraI BO</t>
         </is>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>D4612</t>
+          <t>L4473</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Sonipat HO</t>
+          <t>Gohana SO</t>
         </is>
       </c>
       <c r="D1047" t="inlineStr"/>
@@ -33951,9 +33927,7 @@
         <v>1</v>
       </c>
       <c r="J1047" t="inlineStr"/>
-      <c r="K1047" t="n">
-        <v>1</v>
-      </c>
+      <c r="K1047" t="inlineStr"/>
       <c r="L1047" t="inlineStr"/>
       <c r="M1047" t="inlineStr"/>
       <c r="N1047" t="inlineStr"/>
@@ -33962,27 +33936,25 @@
     <row r="1048">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>Mohana BO</t>
-        </is>
-      </c>
-      <c r="B1048" t="inlineStr">
-        <is>
-          <t>F9696</t>
-        </is>
-      </c>
-      <c r="C1048" t="inlineStr">
-        <is>
-          <t>Sonipat HO</t>
-        </is>
-      </c>
+          <t>Mundlana SO</t>
+        </is>
+      </c>
+      <c r="B1048" t="n">
+        <v>13130601</v>
+      </c>
+      <c r="C1048" t="inlineStr"/>
       <c r="D1048" t="inlineStr"/>
       <c r="E1048" t="inlineStr"/>
-      <c r="F1048" t="inlineStr"/>
+      <c r="F1048" t="n">
+        <v>0</v>
+      </c>
       <c r="G1048" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H1048" t="inlineStr"/>
-      <c r="I1048" t="inlineStr"/>
+      <c r="I1048" t="n">
+        <v>0</v>
+      </c>
       <c r="J1048" t="inlineStr"/>
       <c r="K1048" t="inlineStr"/>
       <c r="L1048" t="inlineStr"/>
@@ -33993,25 +33965,29 @@
     <row r="1049">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>Murthal SO</t>
-        </is>
-      </c>
-      <c r="B1049" t="n">
-        <v>13102701</v>
-      </c>
-      <c r="C1049" t="inlineStr"/>
+          <t>Nuran Khera BO</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>F7984</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Butana SO</t>
+        </is>
+      </c>
       <c r="D1049" t="inlineStr"/>
       <c r="E1049" t="inlineStr"/>
-      <c r="F1049" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1049" t="inlineStr"/>
+      <c r="F1049" t="inlineStr"/>
+      <c r="G1049" t="n">
+        <v>6</v>
+      </c>
       <c r="H1049" t="inlineStr"/>
       <c r="I1049" t="inlineStr"/>
       <c r="J1049" t="inlineStr"/>
-      <c r="K1049" t="n">
-        <v>3</v>
-      </c>
+      <c r="K1049" t="inlineStr"/>
       <c r="L1049" t="inlineStr"/>
       <c r="M1049" t="inlineStr"/>
       <c r="N1049" t="inlineStr"/>
@@ -34020,25 +33996,29 @@
     <row r="1050">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>Nahri SO</t>
-        </is>
-      </c>
-      <c r="B1050" t="n">
-        <v>13110301</v>
-      </c>
-      <c r="C1050" t="inlineStr"/>
+          <t>Pipli BO</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>J9558</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Kharkhauda SO</t>
+        </is>
+      </c>
       <c r="D1050" t="inlineStr"/>
       <c r="E1050" t="inlineStr"/>
-      <c r="F1050" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1050" t="inlineStr"/>
+      <c r="F1050" t="inlineStr"/>
+      <c r="G1050" t="n">
+        <v>5</v>
+      </c>
       <c r="H1050" t="inlineStr"/>
       <c r="I1050" t="inlineStr"/>
       <c r="J1050" t="inlineStr"/>
-      <c r="K1050" t="n">
-        <v>0</v>
-      </c>
+      <c r="K1050" t="inlineStr"/>
       <c r="L1050" t="inlineStr"/>
       <c r="M1050" t="inlineStr"/>
       <c r="N1050" t="inlineStr"/>
@@ -34047,17 +34027,17 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>Nathupur BO</t>
+          <t>Saragthal BO</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
         <is>
-          <t>L4372</t>
+          <t>A7184</t>
         </is>
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>PSRai SO</t>
+          <t>Kanyagurukul Khanpur SO</t>
         </is>
       </c>
       <c r="D1051" t="inlineStr"/>
@@ -34066,12 +34046,10 @@
       <c r="G1051" t="inlineStr"/>
       <c r="H1051" t="inlineStr"/>
       <c r="I1051" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1051" t="inlineStr"/>
-      <c r="K1051" t="n">
-        <v>1</v>
-      </c>
+      <c r="K1051" t="inlineStr"/>
       <c r="L1051" t="inlineStr"/>
       <c r="M1051" t="inlineStr"/>
       <c r="N1051" t="inlineStr"/>
@@ -34080,80 +34058,98 @@
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>PSRai SO</t>
+          <t>Sonipat HO</t>
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>13102901</v>
+        <v>13100100</v>
       </c>
       <c r="C1052" t="inlineStr"/>
-      <c r="D1052" t="inlineStr"/>
+      <c r="D1052" t="n">
+        <v>2</v>
+      </c>
       <c r="E1052" t="inlineStr"/>
-      <c r="F1052" t="inlineStr"/>
+      <c r="F1052" t="n">
+        <v>1</v>
+      </c>
       <c r="G1052" t="n">
         <v>1</v>
       </c>
       <c r="H1052" t="inlineStr"/>
       <c r="I1052" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J1052" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1052" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L1052" t="inlineStr"/>
       <c r="M1052" t="inlineStr"/>
-      <c r="N1052" t="inlineStr"/>
+      <c r="N1052" t="n">
+        <v>4</v>
+      </c>
       <c r="O1052" t="inlineStr"/>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>Rohat SO Sonipat</t>
-        </is>
-      </c>
-      <c r="B1053" t="n">
-        <v>13140301</v>
-      </c>
+          <t>Total:</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr"/>
       <c r="C1053" t="inlineStr"/>
-      <c r="D1053" t="inlineStr"/>
-      <c r="E1053" t="inlineStr"/>
-      <c r="F1053" t="inlineStr"/>
-      <c r="G1053" t="inlineStr"/>
-      <c r="H1053" t="inlineStr"/>
+      <c r="D1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>63</v>
+      </c>
+      <c r="H1053" t="n">
+        <v>0</v>
+      </c>
       <c r="I1053" t="n">
-        <v>1</v>
-      </c>
-      <c r="J1053" t="inlineStr"/>
-      <c r="K1053" t="inlineStr"/>
-      <c r="L1053" t="inlineStr"/>
-      <c r="M1053" t="inlineStr"/>
-      <c r="N1053" t="inlineStr"/>
-      <c r="O1053" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="J1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1053" t="n">
+        <v>48</v>
+      </c>
+      <c r="L1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1053" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>Sandal Kalan BO</t>
-        </is>
-      </c>
-      <c r="B1054" t="inlineStr">
-        <is>
-          <t>B7818</t>
-        </is>
-      </c>
-      <c r="C1054" t="inlineStr">
-        <is>
-          <t>Sonipat HO</t>
-        </is>
-      </c>
+          <t xml:space="preserve">
+Product Wise A/C Report
+</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr"/>
+      <c r="C1054" t="inlineStr"/>
       <c r="D1054" t="inlineStr"/>
       <c r="E1054" t="inlineStr"/>
-      <c r="F1054" t="n">
-        <v>1</v>
-      </c>
+      <c r="F1054" t="inlineStr"/>
       <c r="G1054" t="inlineStr"/>
       <c r="H1054" t="inlineStr"/>
       <c r="I1054" t="inlineStr"/>
@@ -34167,62 +34163,110 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>Sersa BO</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>A7376</t>
+          <t>SOL ID / BOCODE</t>
         </is>
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Industrial Estate Kundli SO</t>
-        </is>
-      </c>
-      <c r="D1055" t="inlineStr"/>
-      <c r="E1055" t="inlineStr"/>
-      <c r="F1055" t="inlineStr"/>
-      <c r="G1055" t="inlineStr"/>
-      <c r="H1055" t="inlineStr"/>
-      <c r="I1055" t="n">
-        <v>1</v>
-      </c>
-      <c r="J1055" t="inlineStr"/>
-      <c r="K1055" t="n">
-        <v>2</v>
-      </c>
-      <c r="L1055" t="inlineStr"/>
-      <c r="M1055" t="inlineStr"/>
-      <c r="N1055" t="inlineStr"/>
-      <c r="O1055" t="inlineStr"/>
+          <t>SO Name</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>MIS</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>PPFGP</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>SBBAS</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>SBSGP</t>
+        </is>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>SCSS</t>
+        </is>
+      </c>
+      <c r="K1055" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="L1055" t="inlineStr">
+        <is>
+          <t>PRFTS</t>
+        </is>
+      </c>
+      <c r="M1055" t="inlineStr">
+        <is>
+          <t>KVN</t>
+        </is>
+      </c>
+      <c r="N1055" t="inlineStr">
+        <is>
+          <t>NSC8</t>
+        </is>
+      </c>
+      <c r="O1055" t="inlineStr">
+        <is>
+          <t>MSSC</t>
+        </is>
+      </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>Shapur Turk BO</t>
+          <t>AhulanaGannur BO</t>
         </is>
       </c>
       <c r="B1056" t="inlineStr">
         <is>
-          <t>D4614</t>
+          <t>A8170</t>
         </is>
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Sonipat HO</t>
+          <t>Ganaur SO</t>
         </is>
       </c>
       <c r="D1056" t="inlineStr"/>
       <c r="E1056" t="inlineStr"/>
       <c r="F1056" t="inlineStr"/>
       <c r="G1056" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1056" t="inlineStr"/>
-      <c r="I1056" t="inlineStr"/>
+      <c r="I1056" t="n">
+        <v>1</v>
+      </c>
       <c r="J1056" t="inlineStr"/>
-      <c r="K1056" t="inlineStr"/>
+      <c r="K1056" t="n">
+        <v>1</v>
+      </c>
       <c r="L1056" t="inlineStr"/>
       <c r="M1056" t="inlineStr"/>
       <c r="N1056" t="inlineStr"/>
@@ -34231,19 +34275,13 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>Sheikhpura BO</t>
-        </is>
-      </c>
-      <c r="B1057" t="inlineStr">
-        <is>
-          <t>E1661</t>
-        </is>
-      </c>
-      <c r="C1057" t="inlineStr">
-        <is>
-          <t>Ganaur SO</t>
-        </is>
-      </c>
+          <t>Atlas Cycle SO</t>
+        </is>
+      </c>
+      <c r="B1057" t="n">
+        <v>13100101</v>
+      </c>
+      <c r="C1057" t="inlineStr"/>
       <c r="D1057" t="inlineStr"/>
       <c r="E1057" t="inlineStr"/>
       <c r="F1057" t="inlineStr"/>
@@ -34251,42 +34289,40 @@
         <v>1</v>
       </c>
       <c r="H1057" t="inlineStr"/>
-      <c r="I1057" t="inlineStr"/>
+      <c r="I1057" t="n">
+        <v>2</v>
+      </c>
       <c r="J1057" t="inlineStr"/>
-      <c r="K1057" t="n">
-        <v>3</v>
-      </c>
+      <c r="K1057" t="inlineStr"/>
       <c r="L1057" t="inlineStr"/>
       <c r="M1057" t="inlineStr"/>
-      <c r="N1057" t="inlineStr"/>
+      <c r="N1057" t="n">
+        <v>1</v>
+      </c>
       <c r="O1057" t="inlineStr"/>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>Sitawali BO</t>
-        </is>
-      </c>
-      <c r="B1058" t="inlineStr">
-        <is>
-          <t>L8606</t>
-        </is>
-      </c>
-      <c r="C1058" t="inlineStr">
-        <is>
-          <t>Juan SO</t>
-        </is>
-      </c>
+          <t>Bahalgarh SO</t>
+        </is>
+      </c>
+      <c r="B1058" t="n">
+        <v>13102101</v>
+      </c>
+      <c r="C1058" t="inlineStr"/>
       <c r="D1058" t="inlineStr"/>
       <c r="E1058" t="inlineStr"/>
       <c r="F1058" t="inlineStr"/>
-      <c r="G1058" t="inlineStr"/>
+      <c r="G1058" t="n">
+        <v>0</v>
+      </c>
       <c r="H1058" t="inlineStr"/>
-      <c r="I1058" t="inlineStr"/>
+      <c r="I1058" t="n">
+        <v>0</v>
+      </c>
       <c r="J1058" t="inlineStr"/>
-      <c r="K1058" t="n">
-        <v>12</v>
-      </c>
+      <c r="K1058" t="inlineStr"/>
       <c r="L1058" t="inlineStr"/>
       <c r="M1058" t="inlineStr"/>
       <c r="N1058" t="inlineStr"/>
@@ -34295,24 +34331,28 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>Sonipat Mandi SO</t>
-        </is>
-      </c>
-      <c r="B1059" t="n">
-        <v>13100111</v>
-      </c>
-      <c r="C1059" t="inlineStr"/>
+          <t>Bayanpur BO</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>B7816</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Sonipat HO</t>
+        </is>
+      </c>
       <c r="D1059" t="inlineStr"/>
       <c r="E1059" t="inlineStr"/>
       <c r="F1059" t="inlineStr"/>
       <c r="G1059" t="inlineStr"/>
       <c r="H1059" t="inlineStr"/>
-      <c r="I1059" t="n">
-        <v>1</v>
-      </c>
+      <c r="I1059" t="inlineStr"/>
       <c r="J1059" t="inlineStr"/>
       <c r="K1059" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L1059" t="inlineStr"/>
       <c r="M1059" t="inlineStr"/>
@@ -34322,28 +34362,26 @@
     <row r="1060">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>Tharuoldepur BO</t>
-        </is>
-      </c>
-      <c r="B1060" t="inlineStr">
-        <is>
-          <t>F9697</t>
-        </is>
-      </c>
-      <c r="C1060" t="inlineStr">
-        <is>
-          <t>Sonipat HO</t>
-        </is>
-      </c>
+          <t>Bhatgaon SO Sonipat</t>
+        </is>
+      </c>
+      <c r="B1060" t="n">
+        <v>13102201</v>
+      </c>
+      <c r="C1060" t="inlineStr"/>
       <c r="D1060" t="inlineStr"/>
       <c r="E1060" t="inlineStr"/>
       <c r="F1060" t="inlineStr"/>
-      <c r="G1060" t="inlineStr"/>
+      <c r="G1060" t="n">
+        <v>2</v>
+      </c>
       <c r="H1060" t="inlineStr"/>
-      <c r="I1060" t="inlineStr"/>
+      <c r="I1060" t="n">
+        <v>2</v>
+      </c>
       <c r="J1060" t="inlineStr"/>
       <c r="K1060" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L1060" t="inlineStr"/>
       <c r="M1060" t="inlineStr"/>
@@ -34353,17 +34391,17 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>Tihar Bagru BO</t>
+          <t>Bindroli BO</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
         <is>
-          <t>L8182</t>
+          <t>M0952</t>
         </is>
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Bhatgaon SO Sonipat</t>
+          <t>Rohat SO Sonipat</t>
         </is>
       </c>
       <c r="D1061" t="inlineStr"/>
@@ -34384,45 +34422,990 @@
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
+          <t>Bohla BO</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>L8602</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Juan SO</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr"/>
+      <c r="E1062" t="inlineStr"/>
+      <c r="F1062" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1062" t="inlineStr"/>
+      <c r="H1062" t="inlineStr"/>
+      <c r="I1062" t="inlineStr"/>
+      <c r="J1062" t="inlineStr"/>
+      <c r="K1062" t="inlineStr"/>
+      <c r="L1062" t="inlineStr"/>
+      <c r="M1062" t="inlineStr"/>
+      <c r="N1062" t="inlineStr"/>
+      <c r="O1062" t="inlineStr"/>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>Datauli BO</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>D3377</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Ganaur SO</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr"/>
+      <c r="E1063" t="inlineStr"/>
+      <c r="F1063" t="inlineStr"/>
+      <c r="G1063" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1063" t="inlineStr"/>
+      <c r="I1063" t="inlineStr"/>
+      <c r="J1063" t="inlineStr"/>
+      <c r="K1063" t="inlineStr"/>
+      <c r="L1063" t="inlineStr"/>
+      <c r="M1063" t="inlineStr"/>
+      <c r="N1063" t="inlineStr"/>
+      <c r="O1063" t="inlineStr"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>Ganaur City SO</t>
+        </is>
+      </c>
+      <c r="B1064" t="n">
+        <v>13110101</v>
+      </c>
+      <c r="C1064" t="inlineStr"/>
+      <c r="D1064" t="inlineStr"/>
+      <c r="E1064" t="inlineStr"/>
+      <c r="F1064" t="inlineStr"/>
+      <c r="G1064" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1064" t="inlineStr"/>
+      <c r="I1064" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1064" t="inlineStr"/>
+      <c r="K1064" t="n">
+        <v>4</v>
+      </c>
+      <c r="L1064" t="inlineStr"/>
+      <c r="M1064" t="inlineStr"/>
+      <c r="N1064" t="inlineStr"/>
+      <c r="O1064" t="inlineStr"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>Ganaur SO</t>
+        </is>
+      </c>
+      <c r="B1065" t="n">
+        <v>13110102</v>
+      </c>
+      <c r="C1065" t="inlineStr"/>
+      <c r="D1065" t="inlineStr"/>
+      <c r="E1065" t="inlineStr"/>
+      <c r="F1065" t="inlineStr"/>
+      <c r="G1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1065" t="inlineStr"/>
+      <c r="I1065" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1065" t="inlineStr"/>
+      <c r="K1065" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1065" t="inlineStr"/>
+      <c r="M1065" t="inlineStr"/>
+      <c r="N1065" t="inlineStr"/>
+      <c r="O1065" t="inlineStr"/>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>Gohana Road SO Sonipat</t>
+        </is>
+      </c>
+      <c r="B1066" t="n">
+        <v>13100104</v>
+      </c>
+      <c r="C1066" t="inlineStr"/>
+      <c r="D1066" t="inlineStr"/>
+      <c r="E1066" t="inlineStr"/>
+      <c r="F1066" t="inlineStr"/>
+      <c r="G1066" t="inlineStr"/>
+      <c r="H1066" t="inlineStr"/>
+      <c r="I1066" t="inlineStr"/>
+      <c r="J1066" t="inlineStr"/>
+      <c r="K1066" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1066" t="inlineStr"/>
+      <c r="M1066" t="inlineStr"/>
+      <c r="N1066" t="inlineStr"/>
+      <c r="O1066" t="inlineStr"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>Harsana Kalan BO</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>A0936</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Sonipat HO</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr"/>
+      <c r="E1067" t="inlineStr"/>
+      <c r="F1067" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1067" t="inlineStr"/>
+      <c r="I1067" t="inlineStr"/>
+      <c r="J1067" t="inlineStr"/>
+      <c r="K1067" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1067" t="inlineStr"/>
+      <c r="M1067" t="inlineStr"/>
+      <c r="N1067" t="inlineStr"/>
+      <c r="O1067" t="inlineStr"/>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>Industrial Estate Kundli SO</t>
+        </is>
+      </c>
+      <c r="B1068" t="n">
+        <v>13102801</v>
+      </c>
+      <c r="C1068" t="inlineStr"/>
+      <c r="D1068" t="inlineStr"/>
+      <c r="E1068" t="inlineStr"/>
+      <c r="F1068" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1068" t="inlineStr"/>
+      <c r="I1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1068" t="inlineStr"/>
+      <c r="K1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1068" t="inlineStr"/>
+      <c r="M1068" t="inlineStr"/>
+      <c r="N1068" t="inlineStr"/>
+      <c r="O1068" t="inlineStr"/>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>Jakhauli SO</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>13102301</v>
+      </c>
+      <c r="C1069" t="inlineStr"/>
+      <c r="D1069" t="inlineStr"/>
+      <c r="E1069" t="inlineStr"/>
+      <c r="F1069" t="inlineStr"/>
+      <c r="G1069" t="inlineStr"/>
+      <c r="H1069" t="inlineStr"/>
+      <c r="I1069" t="inlineStr"/>
+      <c r="J1069" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1069" t="inlineStr"/>
+      <c r="L1069" t="inlineStr"/>
+      <c r="M1069" t="inlineStr"/>
+      <c r="N1069" t="inlineStr"/>
+      <c r="O1069" t="inlineStr"/>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>Janti Kalan BO</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>F7688</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Industrial Estate Kundli SO</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr"/>
+      <c r="E1070" t="inlineStr"/>
+      <c r="F1070" t="inlineStr"/>
+      <c r="G1070" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1070" t="inlineStr"/>
+      <c r="I1070" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1070" t="inlineStr"/>
+      <c r="K1070" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1070" t="inlineStr"/>
+      <c r="M1070" t="inlineStr"/>
+      <c r="N1070" t="inlineStr"/>
+      <c r="O1070" t="inlineStr"/>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>Juan SO</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>13102401</v>
+      </c>
+      <c r="C1071" t="inlineStr"/>
+      <c r="D1071" t="inlineStr"/>
+      <c r="E1071" t="inlineStr"/>
+      <c r="F1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1071" t="inlineStr"/>
+      <c r="I1071" t="inlineStr"/>
+      <c r="J1071" t="inlineStr"/>
+      <c r="K1071" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1071" t="inlineStr"/>
+      <c r="M1071" t="inlineStr"/>
+      <c r="N1071" t="inlineStr"/>
+      <c r="O1071" t="inlineStr"/>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>Karewari BO</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>L8603</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Juan SO</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr"/>
+      <c r="E1072" t="inlineStr"/>
+      <c r="F1072" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1072" t="inlineStr"/>
+      <c r="H1072" t="inlineStr"/>
+      <c r="I1072" t="inlineStr"/>
+      <c r="J1072" t="inlineStr"/>
+      <c r="K1072" t="inlineStr"/>
+      <c r="L1072" t="inlineStr"/>
+      <c r="M1072" t="inlineStr"/>
+      <c r="N1072" t="inlineStr"/>
+      <c r="O1072" t="inlineStr"/>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>Kheri Manajat BO</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>M1780</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Nahri SO</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr"/>
+      <c r="E1073" t="inlineStr"/>
+      <c r="F1073" t="inlineStr"/>
+      <c r="G1073" t="inlineStr"/>
+      <c r="H1073" t="inlineStr"/>
+      <c r="I1073" t="inlineStr"/>
+      <c r="J1073" t="inlineStr"/>
+      <c r="K1073" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1073" t="inlineStr"/>
+      <c r="M1073" t="inlineStr"/>
+      <c r="N1073" t="inlineStr"/>
+      <c r="O1073" t="inlineStr"/>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>Khewra BO</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>O0186</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Bahalgarh SO</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr"/>
+      <c r="E1074" t="inlineStr"/>
+      <c r="F1074" t="inlineStr"/>
+      <c r="G1074" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1074" t="inlineStr"/>
+      <c r="I1074" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1074" t="inlineStr"/>
+      <c r="K1074" t="inlineStr"/>
+      <c r="L1074" t="inlineStr"/>
+      <c r="M1074" t="inlineStr"/>
+      <c r="N1074" t="inlineStr"/>
+      <c r="O1074" t="inlineStr"/>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>Khubru BO</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>E1660</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Ganaur SO</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr"/>
+      <c r="E1075" t="inlineStr"/>
+      <c r="F1075" t="inlineStr"/>
+      <c r="G1075" t="inlineStr"/>
+      <c r="H1075" t="inlineStr"/>
+      <c r="I1075" t="inlineStr"/>
+      <c r="J1075" t="inlineStr"/>
+      <c r="K1075" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1075" t="inlineStr"/>
+      <c r="M1075" t="inlineStr"/>
+      <c r="N1075" t="inlineStr"/>
+      <c r="O1075" t="inlineStr"/>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>Lehrara BO</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>C6243</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Sonipat HO</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr"/>
+      <c r="E1076" t="inlineStr"/>
+      <c r="F1076" t="inlineStr"/>
+      <c r="G1076" t="inlineStr"/>
+      <c r="H1076" t="inlineStr"/>
+      <c r="I1076" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1076" t="inlineStr"/>
+      <c r="K1076" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1076" t="inlineStr"/>
+      <c r="M1076" t="inlineStr"/>
+      <c r="N1076" t="inlineStr"/>
+      <c r="O1076" t="inlineStr"/>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>Mandaura BO</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>M1781</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Nahri SO</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr"/>
+      <c r="E1077" t="inlineStr"/>
+      <c r="F1077" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1077" t="inlineStr"/>
+      <c r="H1077" t="inlineStr"/>
+      <c r="I1077" t="inlineStr"/>
+      <c r="J1077" t="inlineStr"/>
+      <c r="K1077" t="inlineStr"/>
+      <c r="L1077" t="inlineStr"/>
+      <c r="M1077" t="inlineStr"/>
+      <c r="N1077" t="inlineStr"/>
+      <c r="O1077" t="inlineStr"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>Mehlana BO</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>D4612</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Sonipat HO</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr"/>
+      <c r="E1078" t="inlineStr"/>
+      <c r="F1078" t="inlineStr"/>
+      <c r="G1078" t="inlineStr"/>
+      <c r="H1078" t="inlineStr"/>
+      <c r="I1078" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1078" t="inlineStr"/>
+      <c r="K1078" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1078" t="inlineStr"/>
+      <c r="M1078" t="inlineStr"/>
+      <c r="N1078" t="inlineStr"/>
+      <c r="O1078" t="inlineStr"/>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>Mohana BO</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>F9696</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Sonipat HO</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr"/>
+      <c r="E1079" t="inlineStr"/>
+      <c r="F1079" t="inlineStr"/>
+      <c r="G1079" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1079" t="inlineStr"/>
+      <c r="I1079" t="inlineStr"/>
+      <c r="J1079" t="inlineStr"/>
+      <c r="K1079" t="inlineStr"/>
+      <c r="L1079" t="inlineStr"/>
+      <c r="M1079" t="inlineStr"/>
+      <c r="N1079" t="inlineStr"/>
+      <c r="O1079" t="inlineStr"/>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>Murthal SO</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>13102701</v>
+      </c>
+      <c r="C1080" t="inlineStr"/>
+      <c r="D1080" t="inlineStr"/>
+      <c r="E1080" t="inlineStr"/>
+      <c r="F1080" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1080" t="inlineStr"/>
+      <c r="H1080" t="inlineStr"/>
+      <c r="I1080" t="inlineStr"/>
+      <c r="J1080" t="inlineStr"/>
+      <c r="K1080" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1080" t="inlineStr"/>
+      <c r="M1080" t="inlineStr"/>
+      <c r="N1080" t="inlineStr"/>
+      <c r="O1080" t="inlineStr"/>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>Nahri SO</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>13110301</v>
+      </c>
+      <c r="C1081" t="inlineStr"/>
+      <c r="D1081" t="inlineStr"/>
+      <c r="E1081" t="inlineStr"/>
+      <c r="F1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1081" t="inlineStr"/>
+      <c r="H1081" t="inlineStr"/>
+      <c r="I1081" t="inlineStr"/>
+      <c r="J1081" t="inlineStr"/>
+      <c r="K1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1081" t="inlineStr"/>
+      <c r="M1081" t="inlineStr"/>
+      <c r="N1081" t="inlineStr"/>
+      <c r="O1081" t="inlineStr"/>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>Nathupur BO</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>L4372</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>PSRai SO</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr"/>
+      <c r="E1082" t="inlineStr"/>
+      <c r="F1082" t="inlineStr"/>
+      <c r="G1082" t="inlineStr"/>
+      <c r="H1082" t="inlineStr"/>
+      <c r="I1082" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1082" t="inlineStr"/>
+      <c r="K1082" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1082" t="inlineStr"/>
+      <c r="M1082" t="inlineStr"/>
+      <c r="N1082" t="inlineStr"/>
+      <c r="O1082" t="inlineStr"/>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>PSRai SO</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>13102901</v>
+      </c>
+      <c r="C1083" t="inlineStr"/>
+      <c r="D1083" t="inlineStr"/>
+      <c r="E1083" t="inlineStr"/>
+      <c r="F1083" t="inlineStr"/>
+      <c r="G1083" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1083" t="inlineStr"/>
+      <c r="I1083" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1083" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1083" t="inlineStr"/>
+      <c r="M1083" t="inlineStr"/>
+      <c r="N1083" t="inlineStr"/>
+      <c r="O1083" t="inlineStr"/>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>Rohat SO Sonipat</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>13140301</v>
+      </c>
+      <c r="C1084" t="inlineStr"/>
+      <c r="D1084" t="inlineStr"/>
+      <c r="E1084" t="inlineStr"/>
+      <c r="F1084" t="inlineStr"/>
+      <c r="G1084" t="inlineStr"/>
+      <c r="H1084" t="inlineStr"/>
+      <c r="I1084" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1084" t="inlineStr"/>
+      <c r="K1084" t="inlineStr"/>
+      <c r="L1084" t="inlineStr"/>
+      <c r="M1084" t="inlineStr"/>
+      <c r="N1084" t="inlineStr"/>
+      <c r="O1084" t="inlineStr"/>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>Sandal Kalan BO</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>B7818</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Sonipat HO</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr"/>
+      <c r="E1085" t="inlineStr"/>
+      <c r="F1085" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1085" t="inlineStr"/>
+      <c r="H1085" t="inlineStr"/>
+      <c r="I1085" t="inlineStr"/>
+      <c r="J1085" t="inlineStr"/>
+      <c r="K1085" t="inlineStr"/>
+      <c r="L1085" t="inlineStr"/>
+      <c r="M1085" t="inlineStr"/>
+      <c r="N1085" t="inlineStr"/>
+      <c r="O1085" t="inlineStr"/>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Sersa BO</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>A7376</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Industrial Estate Kundli SO</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr"/>
+      <c r="E1086" t="inlineStr"/>
+      <c r="F1086" t="inlineStr"/>
+      <c r="G1086" t="inlineStr"/>
+      <c r="H1086" t="inlineStr"/>
+      <c r="I1086" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1086" t="inlineStr"/>
+      <c r="K1086" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1086" t="inlineStr"/>
+      <c r="M1086" t="inlineStr"/>
+      <c r="N1086" t="inlineStr"/>
+      <c r="O1086" t="inlineStr"/>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>Shapur Turk BO</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>D4614</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Sonipat HO</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr"/>
+      <c r="E1087" t="inlineStr"/>
+      <c r="F1087" t="inlineStr"/>
+      <c r="G1087" t="n">
+        <v>2</v>
+      </c>
+      <c r="H1087" t="inlineStr"/>
+      <c r="I1087" t="inlineStr"/>
+      <c r="J1087" t="inlineStr"/>
+      <c r="K1087" t="inlineStr"/>
+      <c r="L1087" t="inlineStr"/>
+      <c r="M1087" t="inlineStr"/>
+      <c r="N1087" t="inlineStr"/>
+      <c r="O1087" t="inlineStr"/>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>Sheikhpura BO</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>E1661</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Ganaur SO</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr"/>
+      <c r="E1088" t="inlineStr"/>
+      <c r="F1088" t="inlineStr"/>
+      <c r="G1088" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1088" t="inlineStr"/>
+      <c r="I1088" t="inlineStr"/>
+      <c r="J1088" t="inlineStr"/>
+      <c r="K1088" t="n">
+        <v>3</v>
+      </c>
+      <c r="L1088" t="inlineStr"/>
+      <c r="M1088" t="inlineStr"/>
+      <c r="N1088" t="inlineStr"/>
+      <c r="O1088" t="inlineStr"/>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>Sitawali BO</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>L8606</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Juan SO</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr"/>
+      <c r="E1089" t="inlineStr"/>
+      <c r="F1089" t="inlineStr"/>
+      <c r="G1089" t="inlineStr"/>
+      <c r="H1089" t="inlineStr"/>
+      <c r="I1089" t="inlineStr"/>
+      <c r="J1089" t="inlineStr"/>
+      <c r="K1089" t="n">
+        <v>12</v>
+      </c>
+      <c r="L1089" t="inlineStr"/>
+      <c r="M1089" t="inlineStr"/>
+      <c r="N1089" t="inlineStr"/>
+      <c r="O1089" t="inlineStr"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>Sonipat Mandi SO</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>13100111</v>
+      </c>
+      <c r="C1090" t="inlineStr"/>
+      <c r="D1090" t="inlineStr"/>
+      <c r="E1090" t="inlineStr"/>
+      <c r="F1090" t="inlineStr"/>
+      <c r="G1090" t="inlineStr"/>
+      <c r="H1090" t="inlineStr"/>
+      <c r="I1090" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1090" t="inlineStr"/>
+      <c r="K1090" t="n">
+        <v>2</v>
+      </c>
+      <c r="L1090" t="inlineStr"/>
+      <c r="M1090" t="inlineStr"/>
+      <c r="N1090" t="inlineStr"/>
+      <c r="O1090" t="inlineStr"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>Tharuoldepur BO</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>F9697</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Sonipat HO</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr"/>
+      <c r="E1091" t="inlineStr"/>
+      <c r="F1091" t="inlineStr"/>
+      <c r="G1091" t="inlineStr"/>
+      <c r="H1091" t="inlineStr"/>
+      <c r="I1091" t="inlineStr"/>
+      <c r="J1091" t="inlineStr"/>
+      <c r="K1091" t="n">
+        <v>1</v>
+      </c>
+      <c r="L1091" t="inlineStr"/>
+      <c r="M1091" t="inlineStr"/>
+      <c r="N1091" t="inlineStr"/>
+      <c r="O1091" t="inlineStr"/>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>Tihar Bagru BO</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>L8182</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Bhatgaon SO Sonipat</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr"/>
+      <c r="E1092" t="inlineStr"/>
+      <c r="F1092" t="inlineStr"/>
+      <c r="G1092" t="inlineStr"/>
+      <c r="H1092" t="inlineStr"/>
+      <c r="I1092" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1092" t="inlineStr"/>
+      <c r="K1092" t="inlineStr"/>
+      <c r="L1092" t="inlineStr"/>
+      <c r="M1092" t="inlineStr"/>
+      <c r="N1092" t="inlineStr"/>
+      <c r="O1092" t="inlineStr"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
           <t>Total:</t>
         </is>
       </c>
-      <c r="B1062" t="inlineStr"/>
-      <c r="C1062" t="inlineStr"/>
-      <c r="D1062" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1062" t="n">
-        <v>0</v>
-      </c>
-      <c r="F1062" t="n">
+      <c r="B1093" t="inlineStr"/>
+      <c r="C1093" t="inlineStr"/>
+      <c r="D1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1093" t="n">
         <v>7</v>
       </c>
-      <c r="G1062" t="n">
+      <c r="G1093" t="n">
         <v>29</v>
       </c>
-      <c r="H1062" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1062" t="n">
+      <c r="H1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1093" t="n">
         <v>15</v>
       </c>
-      <c r="J1062" t="n">
-        <v>1</v>
-      </c>
-      <c r="K1062" t="n">
+      <c r="J1093" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1093" t="n">
         <v>35</v>
       </c>
-      <c r="L1062" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1062" t="n">
-        <v>0</v>
-      </c>
-      <c r="N1062" t="n">
-        <v>1</v>
-      </c>
-      <c r="O1062" t="n">
+      <c r="L1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1093" t="n">
+        <v>1</v>
+      </c>
+      <c r="O1093" t="n">
         <v>0</v>
       </c>
     </row>
